--- a/data/class.xlsx
+++ b/data/class.xlsx
@@ -5,17 +5,20 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fast Computer\OneDrive\Desktop\folder\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arsalan Ashfaque\Dropbox\Arsalan-Tahir\School Deveopment\School online upgrade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7443AD0-6802-4686-8A20-8679FC00DE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018DF012-CEF1-4348-B59E-A4B9A5780CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$CA$68</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="290">
   <si>
     <t>Roll No</t>
   </si>
@@ -893,7 +896,28 @@
     <t>NA</t>
   </si>
   <si>
-    <t>2025-25</t>
+    <t>1st</t>
+  </si>
+  <si>
+    <t>2nd</t>
+  </si>
+  <si>
+    <t>3rd</t>
+  </si>
+  <si>
+    <t>4th</t>
+  </si>
+  <si>
+    <t>5th</t>
+  </si>
+  <si>
+    <t>6th</t>
+  </si>
+  <si>
+    <t>7th</t>
+  </si>
+  <si>
+    <t>8th</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1025,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1022,17 +1046,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1086,31 +1099,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1120,6 +1109,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1460,71 +1473,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CA68"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="2"/>
-    <col min="2" max="2" width="23.08203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.69921875" style="2"/>
+    <col min="2" max="2" width="23.09765625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.796875" style="2" customWidth="1"/>
     <col min="4" max="4" width="23.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.69921875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.69921875" style="2" customWidth="1"/>
     <col min="7" max="7" width="36" style="2" customWidth="1"/>
     <col min="8" max="8" width="17" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="2"/>
-    <col min="10" max="10" width="29.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.69921875" style="2"/>
+    <col min="10" max="10" width="29.296875" style="2" customWidth="1"/>
     <col min="11" max="11" width="10" style="1" customWidth="1"/>
-    <col min="12" max="14" width="8.6640625" style="1"/>
-    <col min="15" max="15" width="18.58203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="16.25" style="1" customWidth="1"/>
+    <col min="12" max="14" width="8.69921875" style="1"/>
+    <col min="15" max="15" width="18.59765625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="16.19921875" style="1" customWidth="1"/>
     <col min="17" max="17" width="14" style="1" customWidth="1"/>
-    <col min="18" max="18" width="16.58203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.08203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.58203125" style="1" customWidth="1"/>
-    <col min="21" max="22" width="8.6640625" style="1"/>
-    <col min="23" max="23" width="13.58203125" style="1" customWidth="1"/>
-    <col min="24" max="26" width="8.6640625" style="1"/>
-    <col min="27" max="27" width="41.1640625" style="1" customWidth="1"/>
-    <col min="28" max="28" width="20.08203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="16.59765625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.09765625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.59765625" style="1" customWidth="1"/>
+    <col min="21" max="22" width="8.69921875" style="1"/>
+    <col min="23" max="23" width="13.59765625" style="1" customWidth="1"/>
+    <col min="24" max="26" width="8.69921875" style="1"/>
+    <col min="27" max="27" width="41.19921875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="20.09765625" style="1" customWidth="1"/>
     <col min="29" max="29" width="16.5" style="1" customWidth="1"/>
-    <col min="30" max="30" width="12.33203125" style="1" customWidth="1"/>
-    <col min="31" max="32" width="10.83203125" style="1" customWidth="1"/>
+    <col min="30" max="30" width="12.296875" style="1" customWidth="1"/>
+    <col min="31" max="32" width="10.796875" style="1" customWidth="1"/>
     <col min="33" max="33" width="11" style="1" customWidth="1"/>
     <col min="34" max="34" width="9.5" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.58203125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="9.33203125" style="1" customWidth="1"/>
-    <col min="37" max="47" width="8.6640625" style="1"/>
-    <col min="48" max="16384" width="8.6640625" style="2"/>
+    <col min="35" max="35" width="8.59765625" style="1" customWidth="1"/>
+    <col min="36" max="36" width="9.296875" style="1" customWidth="1"/>
+    <col min="37" max="47" width="8.69921875" style="1"/>
+    <col min="48" max="16384" width="8.69921875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:79" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="20" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -1735,29 +1748,35 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A2" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="J2" s="2" t="str">
+      <c r="F2" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="22" t="str">
         <f>IF(AI2&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI2&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI2&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI2&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI2&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -1826,29 +1845,35 @@
       <c r="AT2" s="2"/>
       <c r="AU2" s="2"/>
     </row>
-    <row r="3" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A3" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="F3" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I3" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="2" t="str">
+      <c r="J3" s="22" t="str">
         <f t="shared" ref="J3:J19" si="0">IF(AI3&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI3&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI3&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI3&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI3&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -1917,29 +1942,35 @@
       <c r="AT3" s="2"/>
       <c r="AU3" s="2"/>
     </row>
-    <row r="4" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="F4" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I4" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J4" s="2" t="str">
+      <c r="J4" s="22" t="str">
         <f>IF(AI4&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI4&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI4&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI4&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI4&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2008,29 +2039,35 @@
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
     </row>
-    <row r="5" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I5" s="2" t="s">
+      <c r="F5" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I5" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J5" s="2" t="str">
+      <c r="J5" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2099,29 +2136,35 @@
       <c r="AT5" s="2"/>
       <c r="AU5" s="2"/>
     </row>
-    <row r="6" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="17">
+      <c r="F6" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H6" s="23">
         <v>45666</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="2" t="str">
+      <c r="J6" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2190,35 +2233,35 @@
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
     </row>
-    <row r="7" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A7" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="23">
         <v>45666</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J7" s="2" t="str">
+      <c r="J7" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2287,29 +2330,35 @@
       <c r="AT7" s="2"/>
       <c r="AU7" s="2"/>
     </row>
-    <row r="8" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="F8" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I8" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J8" s="2" t="str">
+      <c r="J8" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2378,35 +2427,35 @@
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
     </row>
-    <row r="9" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="23">
         <v>45666</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J9" s="2" t="str">
+      <c r="J9" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2475,29 +2524,35 @@
       <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
     </row>
-    <row r="10" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I10" s="2" t="s">
+      <c r="F10" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I10" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J10" s="2" t="str">
+      <c r="J10" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2566,29 +2621,35 @@
       <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
     </row>
-    <row r="11" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I11" s="2" t="s">
+      <c r="E11" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I11" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J11" s="2" t="str">
+      <c r="J11" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2657,29 +2718,33 @@
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
     </row>
-    <row r="12" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:79" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="J12" s="2" t="str">
+      <c r="F12" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2748,26 +2813,31 @@
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
     </row>
-    <row r="13" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:79" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="C13" s="22"/>
+      <c r="D13" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="J13" s="2" t="str">
+      <c r="F13" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2836,29 +2906,35 @@
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
     </row>
-    <row r="14" spans="1:79" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:79" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I14" s="2" t="s">
+      <c r="F14" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I14" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J14" s="2" t="str">
+      <c r="J14" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2927,29 +3003,35 @@
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
     </row>
-    <row r="15" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="22" t="s">
         <v>69</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>281</v>
       </c>
       <c r="H15" s="7">
         <v>45873</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J15" s="2" t="str">
+      <c r="J15" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -3018,29 +3100,35 @@
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
     </row>
-    <row r="16" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A16" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I16" s="2" t="s">
+      <c r="F16" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I16" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J16" s="2" t="str">
+      <c r="J16" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -3109,29 +3197,35 @@
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
     </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I17" s="2" t="s">
+      <c r="F17" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I17" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J17" s="2" t="str">
+      <c r="J17" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -3200,29 +3294,35 @@
       <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
     </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I18" s="2" t="s">
+      <c r="F18" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I18" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J18" s="2" t="str">
+      <c r="J18" s="22" t="str">
         <f t="shared" si="0"/>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -3291,29 +3391,35 @@
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
     </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I19" s="2" t="s">
+      <c r="F19" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H19" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I19" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J19" s="2" t="str">
+      <c r="J19" s="22" t="str">
         <f t="shared" si="0"/>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -3382,29 +3488,35 @@
       <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
     </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="D20" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="E20" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I20" s="2" t="s">
+      <c r="F20" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I20" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="J20" s="22" t="s">
         <v>127</v>
       </c>
       <c r="K20" s="5"/>
@@ -3445,29 +3557,35 @@
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
     </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="D21" s="2">
-        <v>1</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="D21" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="E21" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I21" s="2" t="s">
+      <c r="F21" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H21" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I21" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" s="22" t="s">
         <v>131</v>
       </c>
       <c r="K21" s="5">
@@ -3528,29 +3646,35 @@
       <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
     </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="D22" s="2">
-        <v>1</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="D22" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="E22" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I22" s="2" t="s">
+      <c r="F22" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I22" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="J22" s="22" t="s">
         <v>136</v>
       </c>
       <c r="K22" s="5">
@@ -3611,34 +3735,40 @@
       <c r="AT22" s="2"/>
       <c r="AU22" s="2"/>
     </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="2">
-        <v>1</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="D23" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="E23" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I23" s="2" t="s">
+      <c r="F23" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I23" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J23" s="22" t="s">
         <v>127</v>
       </c>
       <c r="K23" s="5"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
       <c r="N23" s="2"/>
       <c r="O23" s="5"/>
       <c r="P23" s="2"/>
@@ -3680,17 +3810,18 @@
       <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
     </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="D24" s="2">
-        <v>1</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="C24" s="22"/>
+      <c r="D24" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="E24" s="22" t="s">
         <v>69</v>
       </c>
       <c r="F24" s="9" t="s">
@@ -3702,10 +3833,10 @@
       <c r="H24" s="7">
         <v>44596</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="I24" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="J24" s="22" t="s">
         <v>136</v>
       </c>
       <c r="K24" s="5">
@@ -3766,29 +3897,35 @@
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
     </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A25" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="D25" s="2">
-        <v>2</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="D25" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="E25" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I25" s="2" t="s">
+      <c r="F25" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H25" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I25" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="J25" s="22" t="s">
         <v>131</v>
       </c>
       <c r="K25" s="5">
@@ -3849,29 +3986,35 @@
       <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
     </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A26" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="2">
-        <v>2</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="D26" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="E26" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I26" s="2" t="s">
+      <c r="F26" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H26" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I26" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J26" s="22" t="s">
         <v>148</v>
       </c>
       <c r="K26" s="5">
@@ -3932,29 +4075,35 @@
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
     </row>
-    <row r="27" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A27" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="D27" s="2">
-        <v>2</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="D27" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="E27" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I27" s="2" t="s">
+      <c r="F27" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I27" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="J27" s="22" t="s">
         <v>148</v>
       </c>
       <c r="K27" s="5">
@@ -4015,29 +4164,35 @@
       <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
     </row>
-    <row r="28" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A28" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="D28" s="2">
-        <v>2</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="D28" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="E28" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I28" s="2" t="s">
+      <c r="F28" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I28" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="J28" s="22" t="s">
         <v>131</v>
       </c>
       <c r="K28" s="5">
@@ -4098,29 +4253,35 @@
       <c r="AT28" s="2"/>
       <c r="AU28" s="2"/>
     </row>
-    <row r="29" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A29" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D29" s="2">
-        <v>2</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="D29" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="E29" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I29" s="2" t="s">
+      <c r="F29" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H29" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I29" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="J29" s="22" t="s">
         <v>158</v>
       </c>
       <c r="K29" s="5">
@@ -4181,35 +4342,35 @@
       <c r="AT29" s="2"/>
       <c r="AU29" s="2"/>
     </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A30" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="D30" s="2">
-        <v>2</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="D30" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="E30" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="F30" s="18" t="s">
+      <c r="F30" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="G30" s="19" t="s">
+      <c r="G30" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="H30" s="20">
+      <c r="H30" s="25">
         <v>45720</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="I30" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="J30" s="22" t="s">
         <v>158</v>
       </c>
       <c r="K30" s="5">
@@ -4270,35 +4431,35 @@
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
     </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A31" s="21" t="s">
+    <row r="31" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A31" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D31" s="2">
-        <v>2</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="D31" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="E31" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="F31" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="G31" s="19" t="s">
+      <c r="G31" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="H31" s="20">
+      <c r="H31" s="25">
         <v>44385</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="I31" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="J31" s="22" t="s">
         <v>148</v>
       </c>
       <c r="K31" s="5">
@@ -4359,29 +4520,35 @@
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
     </row>
-    <row r="32" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A32" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="D32" s="2">
-        <v>2</v>
-      </c>
-      <c r="E32" s="2" t="s">
+      <c r="D32" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="E32" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I32" s="2" t="s">
+      <c r="F32" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H32" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I32" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="J32" s="22" t="s">
         <v>127</v>
       </c>
       <c r="K32" s="5">
@@ -4442,29 +4609,35 @@
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
     </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A33" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="D33" s="2">
-        <v>3</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="D33" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="E33" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I33" s="2" t="s">
+      <c r="F33" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G33" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H33" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I33" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J33" s="2" t="str">
+      <c r="J33" s="22" t="str">
         <f>IF(AI33&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI33&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI33&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI33&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI33&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -4529,35 +4702,35 @@
       <c r="AT33" s="2"/>
       <c r="AU33" s="2"/>
     </row>
-    <row r="34" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A34" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="2">
-        <v>3</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="D34" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="E34" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="F34" s="19" t="s">
+      <c r="F34" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="G34" s="19" t="s">
+      <c r="G34" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="H34" s="22" t="s">
+      <c r="H34" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="I34" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J34" s="2" t="str">
+      <c r="J34" s="22" t="str">
         <f t="shared" ref="J34:J35" si="4">IF(AI34&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI34&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI34&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI34&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI34&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -4622,29 +4795,35 @@
       <c r="AT34" s="2"/>
       <c r="AU34" s="2"/>
     </row>
-    <row r="35" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A35" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="2">
-        <v>3</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="D35" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="E35" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I35" s="2" t="s">
+      <c r="F35" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G35" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H35" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I35" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J35" s="2" t="str">
+      <c r="J35" s="22" t="str">
         <f t="shared" si="4"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -4709,29 +4888,35 @@
       <c r="AT35" s="2"/>
       <c r="AU35" s="2"/>
     </row>
-    <row r="36" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A36" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="D36" s="2">
-        <v>4</v>
-      </c>
-      <c r="E36" s="2" t="s">
+      <c r="D36" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="E36" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H36" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I36" s="2" t="s">
+      <c r="F36" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H36" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I36" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J36" s="2" t="str">
+      <c r="J36" s="22" t="str">
         <f>IF(AL36&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL36&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL36&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL36&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL36&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -4798,29 +4983,35 @@
       <c r="AT36" s="2"/>
       <c r="AU36" s="2"/>
     </row>
-    <row r="37" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A37" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="D37" s="2">
-        <v>4</v>
-      </c>
-      <c r="E37" s="2" t="s">
+      <c r="D37" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="E37" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H37" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I37" s="2" t="s">
+      <c r="F37" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G37" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H37" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I37" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J37" s="2" t="str">
+      <c r="J37" s="22" t="str">
         <f t="shared" ref="J37:J40" si="8">IF(AL37&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL37&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL37&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL37&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL37&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -4887,29 +5078,35 @@
       <c r="AT37" s="2"/>
       <c r="AU37" s="2"/>
     </row>
-    <row r="38" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A38" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="D38" s="2">
-        <v>4</v>
-      </c>
-      <c r="E38" s="2" t="s">
+      <c r="D38" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="E38" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I38" s="2" t="s">
+      <c r="F38" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G38" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H38" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I38" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J38" s="2" t="str">
+      <c r="J38" s="22" t="str">
         <f t="shared" si="8"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -4976,35 +5173,35 @@
       <c r="AT38" s="2"/>
       <c r="AU38" s="2"/>
     </row>
-    <row r="39" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B39" s="23" t="s">
+      <c r="B39" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C39" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="D39" s="2">
-        <v>4</v>
-      </c>
-      <c r="E39" s="2" t="s">
+      <c r="D39" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="E39" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="F39" s="22" t="s">
+      <c r="F39" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G39" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="H39" s="20">
+      <c r="H39" s="25">
         <v>45386</v>
       </c>
-      <c r="I39" s="2" t="s">
+      <c r="I39" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J39" s="2" t="str">
+      <c r="J39" s="22" t="str">
         <f t="shared" si="8"/>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -5071,29 +5268,35 @@
       <c r="AT39" s="2"/>
       <c r="AU39" s="2"/>
     </row>
-    <row r="40" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="B40" s="23" t="s">
+      <c r="B40" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="C40" s="23" t="s">
+      <c r="C40" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="D40" s="2">
-        <v>4</v>
-      </c>
-      <c r="E40" s="2" t="s">
+      <c r="D40" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="E40" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H40" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I40" s="2" t="s">
+      <c r="F40" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G40" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H40" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I40" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J40" s="2" t="str">
+      <c r="J40" s="22" t="str">
         <f t="shared" si="8"/>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -5160,35 +5363,35 @@
       <c r="AT40" s="2"/>
       <c r="AU40" s="2"/>
     </row>
-    <row r="41" spans="1:47" ht="20" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:47" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="B41" s="23" t="s">
+      <c r="B41" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="D41" s="2">
-        <v>5</v>
-      </c>
-      <c r="E41" s="2" t="s">
+      <c r="D41" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="E41" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="F41" s="18" t="s">
+      <c r="F41" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="G41" s="22" t="s">
+      <c r="G41" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="H41" s="20">
+      <c r="H41" s="25">
         <v>45386</v>
       </c>
-      <c r="I41" s="2" t="s">
+      <c r="I41" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J41" s="2" t="str">
+      <c r="J41" s="22" t="str">
         <f>IF(AL41&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL41&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL41&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL41&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL41&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -5255,29 +5458,35 @@
       <c r="AT41" s="2"/>
       <c r="AU41" s="2"/>
     </row>
-    <row r="42" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="B42" s="23" t="s">
+      <c r="B42" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="C42" s="23" t="s">
+      <c r="C42" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="D42" s="2">
-        <v>5</v>
-      </c>
-      <c r="E42" s="2" t="s">
+      <c r="D42" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="E42" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H42" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I42" s="2" t="s">
+      <c r="F42" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G42" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H42" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I42" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J42" s="2" t="str">
+      <c r="J42" s="22" t="str">
         <f t="shared" ref="J42:J47" si="12">IF(AL42&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL42&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL42&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL42&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL42&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -5344,29 +5553,35 @@
       <c r="AT42" s="2"/>
       <c r="AU42" s="2"/>
     </row>
-    <row r="43" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C43" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="D43" s="2">
-        <v>5</v>
-      </c>
-      <c r="E43" s="2" t="s">
+      <c r="D43" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="E43" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H43" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I43" s="2" t="s">
+      <c r="F43" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G43" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H43" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I43" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J43" s="2" t="str">
+      <c r="J43" s="22" t="str">
         <f t="shared" si="12"/>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -5433,29 +5648,35 @@
       <c r="AT43" s="2"/>
       <c r="AU43" s="2"/>
     </row>
-    <row r="44" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="C44" s="23" t="s">
+      <c r="C44" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="D44" s="2">
-        <v>5</v>
-      </c>
-      <c r="E44" s="2" t="s">
+      <c r="D44" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="E44" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H44" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I44" s="2" t="s">
+      <c r="F44" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G44" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H44" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I44" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J44" s="2" t="str">
+      <c r="J44" s="22" t="str">
         <f t="shared" si="12"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -5522,29 +5743,35 @@
       <c r="AT44" s="2"/>
       <c r="AU44" s="2"/>
     </row>
-    <row r="45" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C45" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D45" s="2">
-        <v>5</v>
-      </c>
-      <c r="E45" s="2" t="s">
+      <c r="D45" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="E45" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H45" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I45" s="2" t="s">
+      <c r="F45" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G45" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H45" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I45" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J45" s="2" t="str">
+      <c r="J45" s="22" t="str">
         <f t="shared" si="12"/>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -5611,32 +5838,35 @@
       <c r="AT45" s="2"/>
       <c r="AU45" s="2"/>
     </row>
-    <row r="46" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B46" s="23" t="s">
+      <c r="B46" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="C46" s="23" t="s">
+      <c r="C46" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="D46" s="2">
-        <v>5</v>
-      </c>
-      <c r="E46" s="2" t="s">
+      <c r="D46" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="E46" s="22" t="s">
         <v>69</v>
+      </c>
+      <c r="F46" s="22" t="s">
+        <v>281</v>
       </c>
       <c r="G46" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="H46" s="22" t="s">
+      <c r="H46" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="I46" s="2" t="s">
+      <c r="I46" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J46" s="2" t="str">
+      <c r="J46" s="22" t="str">
         <f t="shared" si="12"/>
         <v>Don't lose heart! With extra hard work, you can improve.</v>
       </c>
@@ -5703,29 +5933,35 @@
       <c r="AT46" s="2"/>
       <c r="AU46" s="2"/>
     </row>
-    <row r="47" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="B47" s="24" t="s">
+      <c r="B47" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C47" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="D47" s="2">
-        <v>5</v>
-      </c>
-      <c r="E47" s="2" t="s">
+      <c r="D47" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="E47" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H47" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I47" s="2" t="s">
+      <c r="F47" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G47" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H47" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I47" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J47" s="2" t="str">
+      <c r="J47" s="22" t="str">
         <f t="shared" si="12"/>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -5792,29 +6028,35 @@
       <c r="AT47" s="2"/>
       <c r="AU47" s="2"/>
     </row>
-    <row r="48" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="B48" s="23" t="s">
+      <c r="B48" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="C48" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="D48" s="2">
-        <v>6</v>
-      </c>
-      <c r="E48" s="2" t="s">
+      <c r="D48" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="E48" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H48" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I48" s="2" t="s">
+      <c r="F48" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G48" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H48" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I48" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J48" s="2" t="str">
+      <c r="J48" s="22" t="str">
         <f>IF(AM48&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AM48&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AM48&gt;=60, "Well done! You have great potential to achieve even more.", IF(AM48&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AM48&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Don't lose heart! With extra hard work, you can improve.</v>
       </c>
@@ -5881,29 +6123,35 @@
       <c r="AT48" s="2"/>
       <c r="AU48" s="2"/>
     </row>
-    <row r="49" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="B49" s="23" t="s">
+      <c r="B49" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="C49" s="23" t="s">
+      <c r="C49" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="D49" s="2">
-        <v>6</v>
-      </c>
-      <c r="E49" s="2" t="s">
+      <c r="D49" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="E49" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H49" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I49" s="2" t="s">
+      <c r="F49" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G49" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H49" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I49" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J49" s="2" t="str">
+      <c r="J49" s="22" t="str">
         <f t="shared" ref="J49:J53" si="16">IF(AM49&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AM49&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AM49&gt;=60, "Well done! You have great potential to achieve even more.", IF(AM49&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AM49&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -5970,29 +6218,35 @@
       <c r="AT49" s="2"/>
       <c r="AU49" s="2"/>
     </row>
-    <row r="50" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B50" s="23" t="s">
+      <c r="B50" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D50" s="2">
-        <v>6</v>
-      </c>
-      <c r="E50" s="2" t="s">
+      <c r="D50" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="E50" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H50" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I50" s="2" t="s">
+      <c r="F50" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G50" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H50" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I50" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J50" s="2" t="str">
+      <c r="J50" s="22" t="str">
         <f t="shared" si="16"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -6059,29 +6313,35 @@
       <c r="AT50" s="2"/>
       <c r="AU50" s="2"/>
     </row>
-    <row r="51" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="C51" s="23" t="s">
+      <c r="C51" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="D51" s="2">
-        <v>6</v>
-      </c>
-      <c r="E51" s="2" t="s">
+      <c r="D51" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="E51" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H51" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I51" s="2" t="s">
+      <c r="F51" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G51" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H51" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I51" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J51" s="2" t="str">
+      <c r="J51" s="22" t="str">
         <f t="shared" si="16"/>
         <v>Don't lose heart! With extra hard work, you can improve.</v>
       </c>
@@ -6148,29 +6408,35 @@
       <c r="AT51" s="2"/>
       <c r="AU51" s="2"/>
     </row>
-    <row r="52" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="B52" s="25" t="s">
+      <c r="B52" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="C52" s="25" t="s">
+      <c r="C52" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="D52" s="2">
-        <v>6</v>
-      </c>
-      <c r="E52" s="2" t="s">
+      <c r="D52" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="E52" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H52" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I52" s="2" t="s">
+      <c r="F52" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G52" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H52" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I52" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J52" s="2" t="str">
+      <c r="J52" s="22" t="str">
         <f t="shared" si="16"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -6237,20 +6503,20 @@
       <c r="AT52" s="2"/>
       <c r="AU52" s="2"/>
     </row>
-    <row r="53" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="B53" s="23" t="s">
+      <c r="B53" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="C53" s="23" t="s">
+      <c r="C53" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="D53" s="2">
-        <v>6</v>
-      </c>
-      <c r="E53" s="2" t="s">
+      <c r="D53" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="E53" s="22" t="s">
         <v>69</v>
       </c>
       <c r="F53" s="13" t="s">
@@ -6262,10 +6528,10 @@
       <c r="H53" s="14">
         <v>45750</v>
       </c>
-      <c r="I53" s="2" t="s">
+      <c r="I53" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J53" s="2" t="str">
+      <c r="J53" s="22" t="str">
         <f t="shared" si="16"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -6332,29 +6598,35 @@
       <c r="AT53" s="2"/>
       <c r="AU53" s="2"/>
     </row>
-    <row r="54" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B54" s="23" t="s">
+      <c r="B54" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="C54" s="23" t="s">
+      <c r="C54" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D54" s="2">
-        <v>7</v>
-      </c>
-      <c r="E54" s="2" t="s">
+      <c r="D54" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="E54" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H54" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I54" s="2" t="s">
+      <c r="F54" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G54" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H54" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I54" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J54" s="2" t="str">
+      <c r="J54" s="22" t="str">
         <f>IF(AM54&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AM54&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AM54&gt;=60, "Well done! You have great potential to achieve even more.", IF(AM54&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AM54&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Impressive work! Your dedication is truly paying off.</v>
       </c>
@@ -6421,29 +6693,35 @@
       <c r="AT54" s="2"/>
       <c r="AU54" s="2"/>
     </row>
-    <row r="55" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="B55" s="23" t="s">
+      <c r="B55" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="C55" s="23" t="s">
+      <c r="C55" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="D55" s="2">
-        <v>7</v>
-      </c>
-      <c r="E55" s="2" t="s">
+      <c r="D55" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="E55" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H55" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I55" s="2" t="s">
+      <c r="F55" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G55" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H55" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I55" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J55" s="2" t="str">
+      <c r="J55" s="22" t="str">
         <f t="shared" ref="J55:J59" si="20">IF(AM55&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AM55&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AM55&gt;=60, "Well done! You have great potential to achieve even more.", IF(AM55&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AM55&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -6510,32 +6788,35 @@
       <c r="AT55" s="2"/>
       <c r="AU55" s="2"/>
     </row>
-    <row r="56" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="B56" s="23" t="s">
+      <c r="B56" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="D56" s="2">
-        <v>7</v>
-      </c>
-      <c r="E56" s="2" t="s">
+      <c r="D56" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="E56" s="22" t="s">
         <v>69</v>
+      </c>
+      <c r="F56" s="22" t="s">
+        <v>281</v>
       </c>
       <c r="G56" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="H56" s="2" t="s">
+      <c r="H56" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="I56" s="2" t="s">
+      <c r="I56" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J56" s="2" t="str">
+      <c r="J56" s="22" t="str">
         <f t="shared" si="20"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -6602,29 +6883,35 @@
       <c r="AT56" s="2"/>
       <c r="AU56" s="2"/>
     </row>
-    <row r="57" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="B57" s="23" t="s">
+      <c r="B57" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="D57" s="2">
-        <v>7</v>
-      </c>
-      <c r="E57" s="2" t="s">
+      <c r="D57" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="E57" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H57" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I57" s="2" t="s">
+      <c r="F57" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G57" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H57" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I57" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J57" s="2" t="str">
+      <c r="J57" s="22" t="str">
         <f t="shared" si="20"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -6691,29 +6978,35 @@
       <c r="AT57" s="2"/>
       <c r="AU57" s="2"/>
     </row>
-    <row r="58" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="B58" s="23" t="s">
+      <c r="B58" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="D58" s="2">
-        <v>7</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="D58" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="E58" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H58" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I58" s="2" t="s">
+      <c r="F58" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G58" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H58" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I58" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J58" s="2" t="str">
+      <c r="J58" s="22" t="str">
         <f t="shared" si="20"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -6780,35 +7073,35 @@
       <c r="AT58" s="2"/>
       <c r="AU58" s="2"/>
     </row>
-    <row r="59" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="B59" s="24" t="s">
+      <c r="B59" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="C59" s="24" t="s">
+      <c r="C59" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="D59" s="2">
-        <v>7</v>
-      </c>
-      <c r="E59" s="2" t="s">
+      <c r="D59" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="E59" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="F59" s="22" t="s">
         <v>251</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G59" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="H59" s="17">
+      <c r="H59" s="23">
         <v>45327</v>
       </c>
-      <c r="I59" s="2" t="s">
+      <c r="I59" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J59" s="2" t="str">
+      <c r="J59" s="22" t="str">
         <f t="shared" si="20"/>
         <v>Impressive work! Your dedication is truly paying off.</v>
       </c>
@@ -6875,29 +7168,35 @@
       <c r="AT59" s="2"/>
       <c r="AU59" s="2"/>
     </row>
-    <row r="60" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="B60" s="23" t="s">
+      <c r="B60" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D60" s="2">
-        <v>8</v>
-      </c>
-      <c r="E60" s="2" t="s">
+      <c r="D60" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="E60" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H60" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I60" s="2" t="s">
+      <c r="F60" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G60" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H60" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I60" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J60" s="2" t="str">
+      <c r="J60" s="22" t="str">
         <f>IF(AN60&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AN60&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AN60&gt;=60, "Well done! You have great potential to achieve even more.", IF(AN60&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AN60&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -6964,29 +7263,35 @@
       <c r="AT60" s="2"/>
       <c r="AU60" s="2"/>
     </row>
-    <row r="61" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="B61" s="23" t="s">
+      <c r="B61" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="D61" s="2">
-        <v>8</v>
-      </c>
-      <c r="E61" s="2" t="s">
+      <c r="D61" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="E61" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H61" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I61" s="2" t="s">
+      <c r="F61" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G61" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H61" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I61" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J61" s="2" t="str">
+      <c r="J61" s="22" t="str">
         <f t="shared" ref="J61:J66" si="24">IF(AN61&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AN61&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AN61&gt;=60, "Well done! You have great potential to achieve even more.", IF(AN61&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AN61&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -7053,29 +7358,35 @@
       <c r="AT61" s="2"/>
       <c r="AU61" s="2"/>
     </row>
-    <row r="62" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="B62" s="23" t="s">
+      <c r="B62" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="D62" s="2">
-        <v>8</v>
-      </c>
-      <c r="E62" s="2" t="s">
+      <c r="D62" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="E62" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H62" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I62" s="2" t="s">
+      <c r="F62" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G62" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H62" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I62" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J62" s="2" t="str">
+      <c r="J62" s="22" t="str">
         <f t="shared" si="24"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -7142,29 +7453,35 @@
       <c r="AT62" s="2"/>
       <c r="AU62" s="2"/>
     </row>
-    <row r="63" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="B63" s="23" t="s">
+      <c r="B63" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="D63" s="2">
-        <v>8</v>
-      </c>
-      <c r="E63" s="2" t="s">
+      <c r="D63" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="E63" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H63" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I63" s="2" t="s">
+      <c r="F63" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G63" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H63" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I63" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J63" s="2" t="str">
+      <c r="J63" s="22" t="str">
         <f t="shared" si="24"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -7231,20 +7548,20 @@
       <c r="AT63" s="2"/>
       <c r="AU63" s="2"/>
     </row>
-    <row r="64" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="B64" s="23" t="s">
+      <c r="B64" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="D64" s="2">
-        <v>8</v>
-      </c>
-      <c r="E64" s="2" t="s">
+      <c r="D64" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="E64" s="22" t="s">
         <v>69</v>
       </c>
       <c r="F64" s="15" t="s">
@@ -7256,10 +7573,10 @@
       <c r="H64" s="14">
         <v>45750</v>
       </c>
-      <c r="I64" s="2" t="s">
+      <c r="I64" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J64" s="2" t="str">
+      <c r="J64" s="22" t="str">
         <f t="shared" si="24"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -7326,20 +7643,20 @@
       <c r="AT64" s="2"/>
       <c r="AU64" s="2"/>
     </row>
-    <row r="65" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="B65" s="23" t="s">
+      <c r="B65" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="D65" s="2">
-        <v>8</v>
-      </c>
-      <c r="E65" s="2" t="s">
+      <c r="D65" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="E65" s="22" t="s">
         <v>69</v>
       </c>
       <c r="F65" s="10" t="s">
@@ -7348,13 +7665,13 @@
       <c r="G65" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="H65" s="2" t="s">
+      <c r="H65" s="22" t="s">
         <v>272</v>
       </c>
-      <c r="I65" s="2" t="s">
+      <c r="I65" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J65" s="2" t="str">
+      <c r="J65" s="22" t="str">
         <f t="shared" si="24"/>
         <v>Impressive work! Your dedication is truly paying off.</v>
       </c>
@@ -7421,29 +7738,35 @@
       <c r="AT65" s="2"/>
       <c r="AU65" s="2"/>
     </row>
-    <row r="66" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="B66" s="23" t="s">
+      <c r="B66" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="C66" s="23" t="s">
+      <c r="C66" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D66" s="2">
-        <v>8</v>
-      </c>
-      <c r="E66" s="2" t="s">
+      <c r="D66" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="E66" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H66" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I66" s="2" t="s">
+      <c r="F66" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G66" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H66" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I66" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J66" s="2" t="str">
+      <c r="J66" s="22" t="str">
         <f t="shared" si="24"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -7510,29 +7833,35 @@
       <c r="AT66" s="2"/>
       <c r="AU66" s="2"/>
     </row>
-    <row r="67" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="B67" s="24" t="s">
+      <c r="B67" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="C67" s="24" t="s">
+      <c r="C67" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="D67" s="2">
-        <v>8</v>
-      </c>
-      <c r="E67" s="2" t="s">
+      <c r="D67" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="E67" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H67" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I67" s="2" t="s">
+      <c r="F67" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G67" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H67" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I67" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J67" s="2" t="str">
+      <c r="J67" s="22" t="str">
         <f>IF(AL67&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL67&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL67&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL67&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL67&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -7593,29 +7922,35 @@
       <c r="AT67" s="2"/>
       <c r="AU67" s="2"/>
     </row>
-    <row r="68" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="B68" s="23" t="s">
+      <c r="B68" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="C68" s="23" t="s">
+      <c r="C68" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D68" s="2">
-        <v>8</v>
-      </c>
-      <c r="E68" s="2" t="s">
+      <c r="D68" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="E68" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H68" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I68" s="2" t="s">
+      <c r="F68" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G68" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H68" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="I68" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="J68" s="2" t="str">
+      <c r="J68" s="22" t="str">
         <f t="shared" ref="J68" si="28">IF(AL68&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL68&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL68&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL68&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL68&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Impressive work! Your dedication is truly paying off.</v>
       </c>
@@ -7683,6 +8018,7 @@
       <c r="AU68" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:CA68" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="1">
     <mergeCell ref="L23:M23"/>
@@ -7695,9 +8031,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:N27"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="H2" t="s">
         <v>39</v>
       </c>
@@ -7705,7 +8041,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>40</v>
       </c>
@@ -7728,7 +8064,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>47</v>
       </c>
@@ -7748,7 +8084,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>48</v>
       </c>
@@ -7764,15 +8100,15 @@
       <c r="J5" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="27" t="s">
+      <c r="L5" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="M5" s="27"/>
+      <c r="M5" s="19"/>
       <c r="N5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>9</v>
       </c>
@@ -7788,15 +8124,15 @@
       <c r="J6" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="27" t="s">
+      <c r="L6" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="27"/>
+      <c r="M6" s="19"/>
       <c r="N6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -7812,15 +8148,15 @@
       <c r="J7" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="M7" s="27"/>
+      <c r="M7" s="19"/>
       <c r="N7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>50</v>
       </c>
@@ -7836,15 +8172,15 @@
       <c r="J8" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="27" t="s">
+      <c r="L8" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="M8" s="27"/>
+      <c r="M8" s="19"/>
       <c r="N8" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>52</v>
       </c>
@@ -7860,12 +8196,12 @@
       <c r="J9" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="27" t="s">
+      <c r="L9" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="27"/>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="M9" s="19"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>53</v>
       </c>
@@ -7881,12 +8217,12 @@
       <c r="J10" t="s">
         <v>27</v>
       </c>
-      <c r="L10" s="27" t="s">
+      <c r="L10" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="M10" s="27"/>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="M10" s="19"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>55</v>
       </c>
@@ -7902,29 +8238,29 @@
       <c r="J11" t="s">
         <v>26</v>
       </c>
-      <c r="L11" s="27" t="s">
+      <c r="L11" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="27"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="M11" s="19"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
         <v>55</v>
       </c>
       <c r="F12" t="s">
         <v>48</v>
       </c>
-      <c r="L12" s="27" t="s">
+      <c r="L12" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="M12" s="27"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="M12" s="19"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="L13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="6:10" x14ac:dyDescent="0.3">
       <c r="F18" t="s">
         <v>57</v>
       </c>
@@ -7935,7 +8271,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="6:10" x14ac:dyDescent="0.3">
       <c r="F19" t="s">
         <v>59</v>
       </c>
@@ -7946,7 +8282,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="6:10" x14ac:dyDescent="0.3">
       <c r="F20" t="s">
         <v>9</v>
       </c>
@@ -7957,7 +8293,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="6:10" x14ac:dyDescent="0.3">
       <c r="F21" t="s">
         <v>11</v>
       </c>
@@ -7968,7 +8304,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="6:10" x14ac:dyDescent="0.3">
       <c r="F22" t="s">
         <v>50</v>
       </c>
@@ -7979,7 +8315,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="6:10" x14ac:dyDescent="0.3">
       <c r="F23" t="s">
         <v>52</v>
       </c>
@@ -7990,7 +8326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="6:10" x14ac:dyDescent="0.3">
       <c r="F24" t="s">
         <v>25</v>
       </c>
@@ -8001,7 +8337,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="6:10" x14ac:dyDescent="0.3">
       <c r="F25" t="s">
         <v>26</v>
       </c>
@@ -8012,7 +8348,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="6:10" x14ac:dyDescent="0.3">
       <c r="F26" t="s">
         <v>55</v>
       </c>
@@ -8023,7 +8359,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="6:10" x14ac:dyDescent="0.3">
       <c r="F27" t="s">
         <v>27</v>
       </c>

--- a/data/class.xlsx
+++ b/data/class.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arsalan Ashfaque\Dropbox\Arsalan-Tahir\School Deveopment\School online upgrade\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fast Computer\OneDrive\Desktop\folder\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018DF012-CEF1-4348-B59E-A4B9A5780CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98D6DF2-E7D9-4209-93CD-41F9A4B0146A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="292">
   <si>
     <t>Roll No</t>
   </si>
@@ -355,9 +355,6 @@
   </si>
   <si>
     <t>Huria Fatima</t>
-  </si>
-  <si>
-    <t>002525</t>
   </si>
   <si>
     <t xml:space="preserve">Manahil </t>
@@ -918,6 +915,15 @@
   </si>
   <si>
     <t>8th</t>
+  </si>
+  <si>
+    <t>002527</t>
+  </si>
+  <si>
+    <t>002528</t>
+  </si>
+  <si>
+    <t>8 (Arts Group)</t>
   </si>
 </sst>
 </file>
@@ -1052,7 +1058,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1105,10 +1111,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1131,6 +1133,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1473,71 +1482,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CA68"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.69921875" style="2"/>
-    <col min="2" max="2" width="23.09765625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="2"/>
+    <col min="2" max="2" width="23.08203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="2" customWidth="1"/>
     <col min="4" max="4" width="23.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.69921875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.69921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="36" style="2" customWidth="1"/>
     <col min="8" max="8" width="17" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.69921875" style="2"/>
-    <col min="10" max="10" width="29.296875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="2"/>
+    <col min="10" max="10" width="29.33203125" style="2" customWidth="1"/>
     <col min="11" max="11" width="10" style="1" customWidth="1"/>
-    <col min="12" max="14" width="8.69921875" style="1"/>
-    <col min="15" max="15" width="18.59765625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="16.19921875" style="1" customWidth="1"/>
+    <col min="12" max="14" width="8.6640625" style="1"/>
+    <col min="15" max="15" width="18.58203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="16.1640625" style="1" customWidth="1"/>
     <col min="17" max="17" width="14" style="1" customWidth="1"/>
-    <col min="18" max="18" width="16.59765625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.09765625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.59765625" style="1" customWidth="1"/>
-    <col min="21" max="22" width="8.69921875" style="1"/>
-    <col min="23" max="23" width="13.59765625" style="1" customWidth="1"/>
-    <col min="24" max="26" width="8.69921875" style="1"/>
-    <col min="27" max="27" width="41.19921875" style="1" customWidth="1"/>
-    <col min="28" max="28" width="20.09765625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="16.58203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.08203125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.58203125" style="1" customWidth="1"/>
+    <col min="21" max="22" width="8.6640625" style="1"/>
+    <col min="23" max="23" width="13.58203125" style="1" customWidth="1"/>
+    <col min="24" max="26" width="8.6640625" style="1"/>
+    <col min="27" max="27" width="41.1640625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="20.08203125" style="1" customWidth="1"/>
     <col min="29" max="29" width="16.5" style="1" customWidth="1"/>
-    <col min="30" max="30" width="12.296875" style="1" customWidth="1"/>
-    <col min="31" max="32" width="10.796875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="12.33203125" style="1" customWidth="1"/>
+    <col min="31" max="32" width="10.83203125" style="1" customWidth="1"/>
     <col min="33" max="33" width="11" style="1" customWidth="1"/>
     <col min="34" max="34" width="9.5" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.59765625" style="1" customWidth="1"/>
-    <col min="36" max="36" width="9.296875" style="1" customWidth="1"/>
-    <col min="37" max="47" width="8.69921875" style="1"/>
-    <col min="48" max="16384" width="8.69921875" style="2"/>
+    <col min="35" max="35" width="8.58203125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="9.33203125" style="1" customWidth="1"/>
+    <col min="37" max="47" width="8.6640625" style="1"/>
+    <col min="48" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:79" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="18" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -1748,35 +1757,35 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="A2" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I2" s="22" t="s">
+      <c r="F2" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="22" t="str">
+      <c r="J2" s="20" t="str">
         <f>IF(AI2&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI2&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI2&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI2&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI2&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -1845,35 +1854,35 @@
       <c r="AT2" s="2"/>
       <c r="AU2" s="2"/>
     </row>
-    <row r="3" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+    <row r="3" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="A3" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I3" s="22" t="s">
+      <c r="F3" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I3" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="22" t="str">
+      <c r="J3" s="20" t="str">
         <f t="shared" ref="J3:J19" si="0">IF(AI3&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI3&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI3&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI3&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI3&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -1942,35 +1951,35 @@
       <c r="AT3" s="2"/>
       <c r="AU3" s="2"/>
     </row>
-    <row r="4" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+    <row r="4" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="A4" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H4" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I4" s="22" t="s">
+      <c r="F4" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I4" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J4" s="22" t="str">
+      <c r="J4" s="20" t="str">
         <f>IF(AI4&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI4&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI4&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI4&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI4&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2039,35 +2048,35 @@
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
     </row>
-    <row r="5" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+    <row r="5" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="A5" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H5" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I5" s="22" t="s">
+      <c r="F5" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I5" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J5" s="22" t="str">
+      <c r="J5" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2136,35 +2145,35 @@
       <c r="AT5" s="2"/>
       <c r="AU5" s="2"/>
     </row>
-    <row r="6" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="A6" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H6" s="23">
+      <c r="F6" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H6" s="21">
         <v>45666</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="22" t="str">
+      <c r="J6" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2233,35 +2242,35 @@
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
     </row>
-    <row r="7" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+    <row r="7" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="A7" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="G7" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="21">
         <v>45666</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="I7" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J7" s="22" t="str">
+      <c r="J7" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2330,35 +2339,35 @@
       <c r="AT7" s="2"/>
       <c r="AU7" s="2"/>
     </row>
-    <row r="8" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+    <row r="8" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="A8" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H8" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I8" s="22" t="s">
+      <c r="F8" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I8" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J8" s="22" t="str">
+      <c r="J8" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2427,35 +2436,35 @@
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
     </row>
-    <row r="9" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
+    <row r="9" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="A9" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="21">
         <v>45666</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="I9" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J9" s="22" t="str">
+      <c r="J9" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2524,35 +2533,35 @@
       <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
     </row>
-    <row r="10" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="B10" s="22" t="s">
+    <row r="10" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="A10" s="28" t="s">
+        <v>290</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I10" s="22" t="s">
+      <c r="F10" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I10" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J10" s="22" t="str">
+      <c r="J10" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2621,35 +2630,35 @@
       <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
     </row>
-    <row r="11" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+    <row r="11" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="A11" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H11" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I11" s="22" t="s">
+      <c r="F11" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I11" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J11" s="22" t="str">
+      <c r="J11" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2718,33 +2727,35 @@
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
     </row>
-    <row r="12" spans="1:79" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F12" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H12" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22" t="str">
+      <c r="F12" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="J12" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2813,31 +2824,33 @@
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
     </row>
-    <row r="13" spans="1:79" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22" t="s">
+      <c r="C13" s="20"/>
+      <c r="D13" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22" t="str">
+      <c r="F13" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="J13" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2906,35 +2919,35 @@
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
     </row>
-    <row r="14" spans="1:79" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B14" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="C14" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H14" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I14" s="22" t="s">
+      <c r="F14" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I14" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J14" s="22" t="str">
+      <c r="J14" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -3003,35 +3016,35 @@
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
     </row>
-    <row r="15" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+    <row r="15" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="A15" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="C15" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" s="22" t="s">
+      <c r="D15" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>281</v>
+      <c r="F15" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>280</v>
       </c>
       <c r="H15" s="7">
         <v>45873</v>
       </c>
-      <c r="I15" s="22" t="s">
+      <c r="I15" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J15" s="22" t="str">
+      <c r="J15" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -3100,35 +3113,35 @@
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
     </row>
-    <row r="16" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
+    <row r="16" spans="1:79" x14ac:dyDescent="0.35">
+      <c r="A16" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="C16" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="22" t="s">
+      <c r="D16" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G16" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H16" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I16" s="22" t="s">
+      <c r="F16" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I16" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J16" s="22" t="str">
+      <c r="J16" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -3197,35 +3210,35 @@
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
     </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="C17" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" s="22" t="s">
+      <c r="D17" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H17" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I17" s="22" t="s">
+      <c r="F17" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I17" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J17" s="22" t="str">
+      <c r="J17" s="20" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -3294,50 +3307,50 @@
       <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
     </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="C18" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" s="22" t="s">
+      <c r="D18" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G18" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H18" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I18" s="22" t="s">
+      <c r="F18" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I18" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J18" s="22" t="str">
+      <c r="J18" s="20" t="str">
         <f t="shared" si="0"/>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
@@ -3345,7 +3358,7 @@
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
       <c r="U18" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V18" s="2"/>
       <c r="W18" s="2"/>
@@ -3355,16 +3368,16 @@
       <c r="AA18" s="2"/>
       <c r="AB18" s="2"/>
       <c r="AC18" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AD18" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AE18" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AF18" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AG18" s="2"/>
       <c r="AH18" s="2">
@@ -3391,50 +3404,50 @@
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
     </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="C19" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="C19" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="E19" s="22" t="s">
+      <c r="D19" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G19" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H19" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I19" s="22" t="s">
+      <c r="F19" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I19" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J19" s="22" t="str">
+      <c r="J19" s="20" t="str">
         <f t="shared" si="0"/>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
@@ -3442,7 +3455,7 @@
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
       <c r="U19" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
@@ -3452,16 +3465,16 @@
       <c r="AA19" s="2"/>
       <c r="AB19" s="2"/>
       <c r="AC19" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AD19" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AE19" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AF19" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AG19" s="2"/>
       <c r="AH19" s="2">
@@ -3488,36 +3501,36 @@
       <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
     </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A20" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="C20" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="J20" s="20" t="s">
         <v>126</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H20" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I20" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="J20" s="22" t="s">
-        <v>127</v>
       </c>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
@@ -3557,36 +3570,36 @@
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
     </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A21" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="C21" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="D21" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="J21" s="20" t="s">
         <v>130</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H21" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I21" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="J21" s="22" t="s">
-        <v>131</v>
       </c>
       <c r="K21" s="5">
         <v>30</v>
@@ -3632,7 +3645,7 @@
         <v>51.5</v>
       </c>
       <c r="AJ21" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK21" s="2"/>
       <c r="AL21" s="2"/>
@@ -3646,36 +3659,36 @@
       <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
     </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="C22" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="D22" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="J22" s="20" t="s">
         <v>135</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H22" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I22" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="J22" s="22" t="s">
-        <v>136</v>
       </c>
       <c r="K22" s="5">
         <v>32.5</v>
@@ -3721,7 +3734,7 @@
         <v>74.625</v>
       </c>
       <c r="AJ22" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK22" s="2"/>
       <c r="AL22" s="2"/>
@@ -3735,40 +3748,40 @@
       <c r="AT22" s="2"/>
       <c r="AU22" s="2"/>
     </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A23" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B23" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="E23" s="22" t="s">
+      <c r="C23" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="E23" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H23" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I23" s="22" t="s">
+      <c r="F23" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I23" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J23" s="22" t="s">
-        <v>127</v>
+      <c r="J23" s="20" t="s">
+        <v>126</v>
       </c>
       <c r="K23" s="5"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
       <c r="N23" s="2"/>
       <c r="O23" s="5"/>
       <c r="P23" s="2"/>
@@ -3796,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="AJ23" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK23" s="2"/>
       <c r="AL23" s="2"/>
@@ -3810,34 +3823,34 @@
       <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
     </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F24" s="9" t="s">
+      <c r="G24" s="10" t="s">
         <v>141</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>142</v>
       </c>
       <c r="H24" s="7">
         <v>44596</v>
       </c>
-      <c r="I24" s="22" t="s">
+      <c r="I24" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J24" s="22" t="s">
-        <v>136</v>
+      <c r="J24" s="20" t="s">
+        <v>135</v>
       </c>
       <c r="K24" s="5">
         <v>44</v>
@@ -3883,7 +3896,7 @@
         <v>74</v>
       </c>
       <c r="AJ24" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK24" s="2"/>
       <c r="AL24" s="2"/>
@@ -3897,36 +3910,36 @@
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
     </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A25" s="22" t="s">
+    <row r="25" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A25" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="C25" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="C25" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="E25" s="22" t="s">
+      <c r="D25" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="E25" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F25" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H25" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I25" s="22" t="s">
+      <c r="F25" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I25" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J25" s="22" t="s">
-        <v>131</v>
+      <c r="J25" s="20" t="s">
+        <v>130</v>
       </c>
       <c r="K25" s="5">
         <v>42</v>
@@ -3972,7 +3985,7 @@
         <v>54.222222222222229</v>
       </c>
       <c r="AJ25" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK25" s="2"/>
       <c r="AL25" s="2"/>
@@ -3986,36 +3999,36 @@
       <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
     </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A26" s="22" t="s">
+    <row r="26" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A26" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="C26" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="J26" s="20" t="s">
         <v>147</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G26" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H26" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I26" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="J26" s="22" t="s">
-        <v>148</v>
       </c>
       <c r="K26" s="5">
         <v>67</v>
@@ -4061,7 +4074,7 @@
         <v>89.555555555555557</v>
       </c>
       <c r="AJ26" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AK26" s="2"/>
       <c r="AL26" s="2"/>
@@ -4075,36 +4088,36 @@
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
     </row>
-    <row r="27" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A27" s="22" t="s">
+    <row r="27" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A27" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B27" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="C27" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="C27" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="E27" s="22" t="s">
+      <c r="D27" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="E27" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F27" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G27" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I27" s="22" t="s">
+      <c r="F27" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I27" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J27" s="22" t="s">
-        <v>148</v>
+      <c r="J27" s="20" t="s">
+        <v>147</v>
       </c>
       <c r="K27" s="5">
         <v>68</v>
@@ -4150,7 +4163,7 @@
         <v>93.222222222222214</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AK27" s="2"/>
       <c r="AL27" s="2"/>
@@ -4164,36 +4177,36 @@
       <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
     </row>
-    <row r="28" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A28" s="22" t="s">
+    <row r="28" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A28" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="C28" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="C28" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="E28" s="22" t="s">
+      <c r="D28" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="E28" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H28" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I28" s="22" t="s">
+      <c r="F28" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I28" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J28" s="22" t="s">
-        <v>131</v>
+      <c r="J28" s="20" t="s">
+        <v>130</v>
       </c>
       <c r="K28" s="5">
         <v>22</v>
@@ -4239,7 +4252,7 @@
         <v>51.111111111111107</v>
       </c>
       <c r="AJ28" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK28" s="2"/>
       <c r="AL28" s="2"/>
@@ -4253,36 +4266,36 @@
       <c r="AT28" s="2"/>
       <c r="AU28" s="2"/>
     </row>
-    <row r="29" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A29" s="22" t="s">
+    <row r="29" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A29" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="C29" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I29" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="J29" s="20" t="s">
         <v>157</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G29" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H29" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I29" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="J29" s="22" t="s">
-        <v>158</v>
       </c>
       <c r="K29" s="5">
         <v>45</v>
@@ -4328,7 +4341,7 @@
         <v>64.111111111111114</v>
       </c>
       <c r="AJ29" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AK29" s="2"/>
       <c r="AL29" s="2"/>
@@ -4342,36 +4355,36 @@
       <c r="AT29" s="2"/>
       <c r="AU29" s="2"/>
     </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A30" s="22" t="s">
+    <row r="30" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A30" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="C30" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="D30" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="D30" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F30" s="9" t="s">
+      <c r="G30" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="G30" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="H30" s="25">
+      <c r="H30" s="23">
         <v>45720</v>
       </c>
-      <c r="I30" s="22" t="s">
+      <c r="I30" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J30" s="22" t="s">
-        <v>158</v>
+      <c r="J30" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="K30" s="5">
         <v>43</v>
@@ -4417,7 +4430,7 @@
         <v>68.888888888888886</v>
       </c>
       <c r="AJ30" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AK30" s="2"/>
       <c r="AL30" s="2"/>
@@ -4431,36 +4444,36 @@
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
     </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A31" s="26" t="s">
+    <row r="31" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A31" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B31" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="C31" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F31" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="C31" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F31" s="24" t="s">
+      <c r="G31" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="G31" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="H31" s="25">
+      <c r="H31" s="23">
         <v>44385</v>
       </c>
-      <c r="I31" s="22" t="s">
+      <c r="I31" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J31" s="22" t="s">
-        <v>148</v>
+      <c r="J31" s="20" t="s">
+        <v>147</v>
       </c>
       <c r="K31" s="5">
         <v>67.5</v>
@@ -4506,7 +4519,7 @@
         <v>93.333333333333329</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AK31" s="2"/>
       <c r="AL31" s="2"/>
@@ -4520,36 +4533,36 @@
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
     </row>
-    <row r="32" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A32" s="22" t="s">
+    <row r="32" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A32" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="B32" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="B32" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="E32" s="22" t="s">
+      <c r="C32" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="E32" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F32" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G32" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H32" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I32" s="22" t="s">
+      <c r="F32" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I32" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J32" s="22" t="s">
-        <v>127</v>
+      <c r="J32" s="20" t="s">
+        <v>126</v>
       </c>
       <c r="K32" s="5">
         <v>2</v>
@@ -4595,7 +4608,7 @@
         <v>21.888888888888889</v>
       </c>
       <c r="AJ32" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK32" s="2"/>
       <c r="AL32" s="2"/>
@@ -4609,35 +4622,35 @@
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
     </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A33" s="22" t="s">
+    <row r="33" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A33" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="C33" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="C33" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>284</v>
-      </c>
-      <c r="E33" s="22" t="s">
+      <c r="D33" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="E33" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F33" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G33" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H33" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I33" s="22" t="s">
+      <c r="F33" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H33" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I33" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J33" s="22" t="str">
+      <c r="J33" s="20" t="str">
         <f>IF(AI33&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI33&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI33&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI33&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI33&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -4702,35 +4715,35 @@
       <c r="AT33" s="2"/>
       <c r="AU33" s="2"/>
     </row>
-    <row r="34" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A34" s="22" t="s">
+    <row r="34" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A34" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="C34" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="C34" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>284</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F34" s="24" t="s">
+      <c r="G34" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="G34" s="24" t="s">
+      <c r="H34" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="H34" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="I34" s="22" t="s">
+      <c r="I34" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J34" s="22" t="str">
+      <c r="J34" s="20" t="str">
         <f t="shared" ref="J34:J35" si="4">IF(AI34&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI34&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI34&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI34&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI34&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -4795,35 +4808,35 @@
       <c r="AT34" s="2"/>
       <c r="AU34" s="2"/>
     </row>
-    <row r="35" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A35" s="22" t="s">
+    <row r="35" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A35" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="B35" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="B35" s="22" t="s">
-        <v>180</v>
-      </c>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="22" t="s">
-        <v>284</v>
-      </c>
-      <c r="E35" s="22" t="s">
+      <c r="D35" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="E35" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F35" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G35" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H35" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I35" s="22" t="s">
+      <c r="F35" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H35" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I35" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J35" s="22" t="str">
+      <c r="J35" s="20" t="str">
         <f t="shared" si="4"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -4888,35 +4901,35 @@
       <c r="AT35" s="2"/>
       <c r="AU35" s="2"/>
     </row>
-    <row r="36" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A36" s="22" t="s">
+    <row r="36" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A36" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="B36" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="C36" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="C36" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="E36" s="22" t="s">
+      <c r="D36" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="E36" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F36" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G36" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H36" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I36" s="22" t="s">
+      <c r="F36" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I36" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J36" s="22" t="str">
+      <c r="J36" s="20" t="str">
         <f>IF(AL36&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL36&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL36&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL36&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL36&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -4983,35 +4996,35 @@
       <c r="AT36" s="2"/>
       <c r="AU36" s="2"/>
     </row>
-    <row r="37" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A37" s="22" t="s">
+    <row r="37" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A37" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="B37" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="C37" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="C37" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="E37" s="22" t="s">
+      <c r="D37" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="E37" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F37" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G37" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H37" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I37" s="22" t="s">
+      <c r="F37" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I37" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J37" s="22" t="str">
+      <c r="J37" s="20" t="str">
         <f t="shared" ref="J37:J40" si="8">IF(AL37&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL37&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL37&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL37&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL37&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -5078,35 +5091,35 @@
       <c r="AT37" s="2"/>
       <c r="AU37" s="2"/>
     </row>
-    <row r="38" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A38" s="22" t="s">
+    <row r="38" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A38" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="B38" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="B38" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="C38" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="D38" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="E38" s="22" t="s">
+      <c r="C38" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="E38" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F38" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G38" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H38" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I38" s="22" t="s">
+      <c r="F38" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I38" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J38" s="22" t="str">
+      <c r="J38" s="20" t="str">
         <f t="shared" si="8"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -5173,35 +5186,35 @@
       <c r="AT38" s="2"/>
       <c r="AU38" s="2"/>
     </row>
-    <row r="39" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B39" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="C39" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="D39" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F39" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="D39" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F39" s="27" t="s">
+      <c r="G39" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="G39" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="H39" s="25">
+      <c r="H39" s="23">
         <v>45386</v>
       </c>
-      <c r="I39" s="22" t="s">
+      <c r="I39" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J39" s="22" t="str">
+      <c r="J39" s="20" t="str">
         <f t="shared" si="8"/>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -5268,35 +5281,35 @@
       <c r="AT39" s="2"/>
       <c r="AU39" s="2"/>
     </row>
-    <row r="40" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B40" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="C40" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="C40" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="D40" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="E40" s="22" t="s">
+      <c r="D40" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="E40" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F40" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G40" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H40" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I40" s="22" t="s">
+      <c r="F40" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I40" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J40" s="22" t="str">
+      <c r="J40" s="20" t="str">
         <f t="shared" si="8"/>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -5363,35 +5376,35 @@
       <c r="AT40" s="2"/>
       <c r="AU40" s="2"/>
     </row>
-    <row r="41" spans="1:47" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:47" ht="20" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B41" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="C41" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="C41" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="E41" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F41" s="9" t="s">
+      <c r="G41" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="G41" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="H41" s="25">
+      <c r="H41" s="23">
         <v>45386</v>
       </c>
-      <c r="I41" s="22" t="s">
+      <c r="I41" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J41" s="22" t="str">
+      <c r="J41" s="20" t="str">
         <f>IF(AL41&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL41&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL41&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL41&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL41&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -5458,35 +5471,35 @@
       <c r="AT41" s="2"/>
       <c r="AU41" s="2"/>
     </row>
-    <row r="42" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B42" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="C42" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="C42" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D42" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="E42" s="22" t="s">
+      <c r="D42" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="E42" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F42" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G42" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H42" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I42" s="22" t="s">
+      <c r="F42" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I42" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J42" s="22" t="str">
+      <c r="J42" s="20" t="str">
         <f t="shared" ref="J42:J47" si="12">IF(AL42&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL42&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL42&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL42&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL42&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -5553,35 +5566,35 @@
       <c r="AT42" s="2"/>
       <c r="AU42" s="2"/>
     </row>
-    <row r="43" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B43" s="16" t="s">
         <v>204</v>
-      </c>
-      <c r="B43" s="16" t="s">
-        <v>205</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="D43" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="E43" s="22" t="s">
+      <c r="D43" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="E43" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F43" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G43" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H43" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I43" s="22" t="s">
+      <c r="F43" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H43" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I43" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J43" s="22" t="str">
+      <c r="J43" s="20" t="str">
         <f t="shared" si="12"/>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -5648,35 +5661,35 @@
       <c r="AT43" s="2"/>
       <c r="AU43" s="2"/>
     </row>
-    <row r="44" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B44" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="C44" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="C44" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="E44" s="22" t="s">
+      <c r="D44" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="E44" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F44" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G44" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H44" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I44" s="22" t="s">
+      <c r="F44" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H44" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I44" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J44" s="22" t="str">
+      <c r="J44" s="20" t="str">
         <f t="shared" si="12"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -5743,35 +5756,35 @@
       <c r="AT44" s="2"/>
       <c r="AU44" s="2"/>
     </row>
-    <row r="45" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B45" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="C45" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="C45" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="D45" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="E45" s="22" t="s">
+      <c r="D45" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="E45" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F45" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G45" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H45" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I45" s="22" t="s">
+      <c r="F45" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G45" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H45" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I45" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J45" s="22" t="str">
+      <c r="J45" s="20" t="str">
         <f t="shared" si="12"/>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -5838,35 +5851,35 @@
       <c r="AT45" s="2"/>
       <c r="AU45" s="2"/>
     </row>
-    <row r="46" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B46" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="C46" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="D46" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G46" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="D46" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F46" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G46" s="11" t="s">
+      <c r="H46" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="H46" s="27" t="s">
-        <v>216</v>
-      </c>
-      <c r="I46" s="22" t="s">
+      <c r="I46" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J46" s="22" t="str">
+      <c r="J46" s="20" t="str">
         <f t="shared" si="12"/>
         <v>Don't lose heart! With extra hard work, you can improve.</v>
       </c>
@@ -5886,7 +5899,7 @@
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="S46" s="5">
         <v>43.5</v>
@@ -5933,35 +5946,35 @@
       <c r="AT46" s="2"/>
       <c r="AU46" s="2"/>
     </row>
-    <row r="47" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B47" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="C47" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C47" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="E47" s="22" t="s">
+      <c r="D47" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="E47" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F47" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G47" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H47" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I47" s="22" t="s">
+      <c r="F47" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G47" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H47" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I47" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J47" s="22" t="str">
+      <c r="J47" s="20" t="str">
         <f t="shared" si="12"/>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -6028,35 +6041,35 @@
       <c r="AT47" s="2"/>
       <c r="AU47" s="2"/>
     </row>
-    <row r="48" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B48" s="16" t="s">
         <v>74</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="E48" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="E48" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F48" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G48" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H48" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I48" s="22" t="s">
+      <c r="F48" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G48" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H48" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I48" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J48" s="22" t="str">
+      <c r="J48" s="20" t="str">
         <f>IF(AM48&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AM48&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AM48&gt;=60, "Well done! You have great potential to achieve even more.", IF(AM48&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AM48&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Don't lose heart! With extra hard work, you can improve.</v>
       </c>
@@ -6123,35 +6136,35 @@
       <c r="AT48" s="2"/>
       <c r="AU48" s="2"/>
     </row>
-    <row r="49" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B49" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="C49" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="C49" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="E49" s="22" t="s">
+      <c r="D49" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="E49" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F49" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G49" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H49" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I49" s="22" t="s">
+      <c r="F49" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G49" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H49" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I49" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J49" s="22" t="str">
+      <c r="J49" s="20" t="str">
         <f t="shared" ref="J49:J53" si="16">IF(AM49&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AM49&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AM49&gt;=60, "Well done! You have great potential to achieve even more.", IF(AM49&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AM49&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -6218,35 +6231,35 @@
       <c r="AT49" s="2"/>
       <c r="AU49" s="2"/>
     </row>
-    <row r="50" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B50" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="B50" s="16" t="s">
-        <v>225</v>
-      </c>
       <c r="C50" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="E50" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="E50" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F50" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G50" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H50" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I50" s="22" t="s">
+      <c r="F50" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G50" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H50" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I50" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J50" s="22" t="str">
+      <c r="J50" s="20" t="str">
         <f t="shared" si="16"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -6313,35 +6326,35 @@
       <c r="AT50" s="2"/>
       <c r="AU50" s="2"/>
     </row>
-    <row r="51" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B51" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="C51" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="C51" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="D51" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="E51" s="22" t="s">
+      <c r="D51" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="E51" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F51" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G51" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H51" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I51" s="22" t="s">
+      <c r="F51" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G51" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H51" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I51" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J51" s="22" t="str">
+      <c r="J51" s="20" t="str">
         <f t="shared" si="16"/>
         <v>Don't lose heart! With extra hard work, you can improve.</v>
       </c>
@@ -6408,35 +6421,35 @@
       <c r="AT51" s="2"/>
       <c r="AU51" s="2"/>
     </row>
-    <row r="52" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A52" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B52" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="C52" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="C52" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="E52" s="22" t="s">
+      <c r="D52" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="E52" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F52" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G52" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H52" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I52" s="22" t="s">
+      <c r="F52" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G52" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H52" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I52" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J52" s="22" t="str">
+      <c r="J52" s="20" t="str">
         <f t="shared" si="16"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -6503,35 +6516,35 @@
       <c r="AT52" s="2"/>
       <c r="AU52" s="2"/>
     </row>
-    <row r="53" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B53" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="C53" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="D53" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F53" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="C53" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="E53" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F53" s="13" t="s">
+      <c r="G53" s="10" t="s">
         <v>234</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>235</v>
       </c>
       <c r="H53" s="14">
         <v>45750</v>
       </c>
-      <c r="I53" s="22" t="s">
+      <c r="I53" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J53" s="22" t="str">
+      <c r="J53" s="20" t="str">
         <f t="shared" si="16"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -6598,35 +6611,35 @@
       <c r="AT53" s="2"/>
       <c r="AU53" s="2"/>
     </row>
-    <row r="54" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B54" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="B54" s="16" t="s">
-        <v>237</v>
-      </c>
       <c r="C54" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>288</v>
-      </c>
-      <c r="E54" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="E54" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F54" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G54" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H54" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I54" s="22" t="s">
+      <c r="F54" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G54" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H54" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I54" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J54" s="22" t="str">
+      <c r="J54" s="20" t="str">
         <f>IF(AM54&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AM54&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AM54&gt;=60, "Well done! You have great potential to achieve even more.", IF(AM54&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AM54&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Impressive work! Your dedication is truly paying off.</v>
       </c>
@@ -6693,35 +6706,35 @@
       <c r="AT54" s="2"/>
       <c r="AU54" s="2"/>
     </row>
-    <row r="55" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B55" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="C55" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="C55" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>288</v>
-      </c>
-      <c r="E55" s="22" t="s">
+      <c r="D55" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="E55" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F55" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G55" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H55" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I55" s="22" t="s">
+      <c r="F55" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G55" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H55" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I55" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J55" s="22" t="str">
+      <c r="J55" s="20" t="str">
         <f t="shared" ref="J55:J59" si="20">IF(AM55&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AM55&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AM55&gt;=60, "Well done! You have great potential to achieve even more.", IF(AM55&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AM55&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -6788,35 +6801,35 @@
       <c r="AT55" s="2"/>
       <c r="AU55" s="2"/>
     </row>
-    <row r="56" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B56" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="B56" s="16" t="s">
+      <c r="C56" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D56" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F56" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G56" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="C56" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="D56" s="22" t="s">
-        <v>288</v>
-      </c>
-      <c r="E56" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F56" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G56" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="H56" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="I56" s="22" t="s">
+      <c r="H56" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="I56" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J56" s="22" t="str">
+      <c r="J56" s="20" t="str">
         <f t="shared" si="20"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -6883,35 +6896,35 @@
       <c r="AT56" s="2"/>
       <c r="AU56" s="2"/>
     </row>
-    <row r="57" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B57" s="16" t="s">
         <v>244</v>
       </c>
-      <c r="B57" s="16" t="s">
+      <c r="C57" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="C57" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="D57" s="22" t="s">
-        <v>288</v>
-      </c>
-      <c r="E57" s="22" t="s">
+      <c r="D57" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="E57" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F57" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G57" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H57" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I57" s="22" t="s">
+      <c r="F57" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G57" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H57" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I57" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J57" s="22" t="str">
+      <c r="J57" s="20" t="str">
         <f t="shared" si="20"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -6978,35 +6991,35 @@
       <c r="AT57" s="2"/>
       <c r="AU57" s="2"/>
     </row>
-    <row r="58" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="D58" s="22" t="s">
-        <v>288</v>
-      </c>
-      <c r="E58" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="D58" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="E58" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F58" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G58" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H58" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I58" s="22" t="s">
+      <c r="F58" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G58" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H58" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I58" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J58" s="22" t="str">
+      <c r="J58" s="20" t="str">
         <f t="shared" si="20"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -7073,35 +7086,35 @@
       <c r="AT58" s="2"/>
       <c r="AU58" s="2"/>
     </row>
-    <row r="59" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B59" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="C59" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="D59" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F59" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="D59" s="22" t="s">
-        <v>288</v>
-      </c>
-      <c r="E59" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F59" s="22" t="s">
+      <c r="G59" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="G59" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="H59" s="23">
+      <c r="H59" s="21">
         <v>45327</v>
       </c>
-      <c r="I59" s="22" t="s">
+      <c r="I59" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J59" s="22" t="str">
+      <c r="J59" s="20" t="str">
         <f t="shared" si="20"/>
         <v>Impressive work! Your dedication is truly paying off.</v>
       </c>
@@ -7168,35 +7181,35 @@
       <c r="AT59" s="2"/>
       <c r="AU59" s="2"/>
     </row>
-    <row r="60" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B60" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="B60" s="16" t="s">
-        <v>254</v>
-      </c>
       <c r="C60" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="D60" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="E60" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="D60" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="E60" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F60" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G60" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H60" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I60" s="22" t="s">
+      <c r="F60" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G60" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H60" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I60" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J60" s="22" t="str">
+      <c r="J60" s="20" t="str">
         <f>IF(AN60&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AN60&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AN60&gt;=60, "Well done! You have great potential to achieve even more.", IF(AN60&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AN60&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -7263,35 +7276,35 @@
       <c r="AT60" s="2"/>
       <c r="AU60" s="2"/>
     </row>
-    <row r="61" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B61" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="C61" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="C61" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="D61" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="E61" s="22" t="s">
+      <c r="D61" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="E61" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F61" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G61" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H61" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I61" s="22" t="s">
+      <c r="F61" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G61" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I61" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J61" s="22" t="str">
+      <c r="J61" s="20" t="str">
         <f t="shared" ref="J61:J66" si="24">IF(AN61&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AN61&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AN61&gt;=60, "Well done! You have great potential to achieve even more.", IF(AN61&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AN61&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -7358,35 +7371,35 @@
       <c r="AT61" s="2"/>
       <c r="AU61" s="2"/>
     </row>
-    <row r="62" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B62" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="C62" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="C62" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="D62" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="E62" s="22" t="s">
+      <c r="D62" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="E62" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F62" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G62" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H62" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I62" s="22" t="s">
+      <c r="F62" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G62" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H62" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I62" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J62" s="22" t="str">
+      <c r="J62" s="20" t="str">
         <f t="shared" si="24"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -7453,35 +7466,35 @@
       <c r="AT62" s="2"/>
       <c r="AU62" s="2"/>
     </row>
-    <row r="63" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B63" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="C63" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="C63" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="D63" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="E63" s="22" t="s">
+      <c r="D63" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="E63" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F63" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G63" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H63" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I63" s="22" t="s">
+      <c r="F63" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G63" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H63" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I63" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J63" s="22" t="str">
+      <c r="J63" s="20" t="str">
         <f t="shared" si="24"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -7548,35 +7561,35 @@
       <c r="AT63" s="2"/>
       <c r="AU63" s="2"/>
     </row>
-    <row r="64" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="B64" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="C64" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="D64" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F64" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="C64" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="D64" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="E64" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F64" s="15" t="s">
+      <c r="G64" s="10" t="s">
         <v>266</v>
-      </c>
-      <c r="G64" s="10" t="s">
-        <v>267</v>
       </c>
       <c r="H64" s="14">
         <v>45750</v>
       </c>
-      <c r="I64" s="22" t="s">
+      <c r="I64" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J64" s="22" t="str">
+      <c r="J64" s="20" t="str">
         <f t="shared" si="24"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -7643,35 +7656,35 @@
       <c r="AT64" s="2"/>
       <c r="AU64" s="2"/>
     </row>
-    <row r="65" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B65" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="C65" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D65" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F65" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="C65" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="D65" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="E65" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F65" s="10" t="s">
+      <c r="G65" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="G65" s="10" t="s">
+      <c r="H65" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="H65" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="I65" s="22" t="s">
+      <c r="I65" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J65" s="22" t="str">
+      <c r="J65" s="20" t="str">
         <f t="shared" si="24"/>
         <v>Impressive work! Your dedication is truly paying off.</v>
       </c>
@@ -7738,35 +7751,35 @@
       <c r="AT65" s="2"/>
       <c r="AU65" s="2"/>
     </row>
-    <row r="66" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B66" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="C66" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="C66" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="D66" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="E66" s="22" t="s">
+      <c r="D66" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="E66" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F66" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G66" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H66" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I66" s="22" t="s">
+      <c r="F66" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G66" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H66" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I66" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J66" s="22" t="str">
+      <c r="J66" s="20" t="str">
         <f t="shared" si="24"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -7833,35 +7846,35 @@
       <c r="AT66" s="2"/>
       <c r="AU66" s="2"/>
     </row>
-    <row r="67" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B67" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="C67" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="C67" s="16" t="s">
-        <v>278</v>
-      </c>
-      <c r="D67" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="E67" s="22" t="s">
+      <c r="D67" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="E67" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F67" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G67" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H67" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I67" s="22" t="s">
+      <c r="F67" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G67" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H67" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I67" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J67" s="22" t="str">
+      <c r="J67" s="20" t="str">
         <f>IF(AL67&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL67&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL67&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL67&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL67&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -7922,35 +7935,35 @@
       <c r="AT67" s="2"/>
       <c r="AU67" s="2"/>
     </row>
-    <row r="68" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B68" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="B68" s="16" t="s">
-        <v>280</v>
-      </c>
       <c r="C68" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="D68" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="E68" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="D68" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="E68" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F68" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G68" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H68" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I68" s="22" t="s">
+      <c r="F68" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G68" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H68" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I68" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J68" s="22" t="str">
+      <c r="J68" s="20" t="str">
         <f t="shared" ref="J68" si="28">IF(AL68&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL68&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL68&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL68&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL68&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Impressive work! Your dedication is truly paying off.</v>
       </c>
@@ -8031,9 +8044,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:N27"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="H2" t="s">
         <v>39</v>
       </c>
@@ -8041,7 +8054,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>40</v>
       </c>
@@ -8064,7 +8077,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>47</v>
       </c>
@@ -8084,7 +8097,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>48</v>
       </c>
@@ -8100,15 +8113,15 @@
       <c r="J5" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="M5" s="19"/>
+      <c r="M5" s="27"/>
       <c r="N5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>9</v>
       </c>
@@ -8124,15 +8137,15 @@
       <c r="J6" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="19"/>
+      <c r="M6" s="27"/>
       <c r="N6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -8148,15 +8161,15 @@
       <c r="J7" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="M7" s="19"/>
+      <c r="M7" s="27"/>
       <c r="N7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>50</v>
       </c>
@@ -8172,15 +8185,15 @@
       <c r="J8" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="M8" s="19"/>
+      <c r="M8" s="27"/>
       <c r="N8" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>52</v>
       </c>
@@ -8196,12 +8209,12 @@
       <c r="J9" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="19" t="s">
+      <c r="L9" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="19"/>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="M9" s="27"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>53</v>
       </c>
@@ -8217,12 +8230,12 @@
       <c r="J10" t="s">
         <v>27</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="M10" s="19"/>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="M10" s="27"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>55</v>
       </c>
@@ -8238,29 +8251,29 @@
       <c r="J11" t="s">
         <v>26</v>
       </c>
-      <c r="L11" s="19" t="s">
+      <c r="L11" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="19"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="M11" s="27"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="D12" t="s">
         <v>55</v>
       </c>
       <c r="F12" t="s">
         <v>48</v>
       </c>
-      <c r="L12" s="19" t="s">
+      <c r="L12" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="M12" s="19"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="M12" s="27"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="L13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F18" t="s">
         <v>57</v>
       </c>
@@ -8271,7 +8284,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F19" t="s">
         <v>59</v>
       </c>
@@ -8282,7 +8295,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F20" t="s">
         <v>9</v>
       </c>
@@ -8293,7 +8306,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F21" t="s">
         <v>11</v>
       </c>
@@ -8304,7 +8317,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F22" t="s">
         <v>50</v>
       </c>
@@ -8315,7 +8328,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F23" t="s">
         <v>52</v>
       </c>
@@ -8326,7 +8339,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F24" t="s">
         <v>25</v>
       </c>
@@ -8337,7 +8350,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F25" t="s">
         <v>26</v>
       </c>
@@ -8348,7 +8361,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F26" t="s">
         <v>55</v>
       </c>
@@ -8359,7 +8372,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F27" t="s">
         <v>27</v>
       </c>

--- a/data/class.xlsx
+++ b/data/class.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fast Computer\OneDrive\Desktop\folder\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98D6DF2-E7D9-4209-93CD-41F9A4B0146A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55EF55B6-712C-4489-BD71-CD1C9CE25803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="284">
   <si>
     <t>Roll No</t>
   </si>
@@ -893,30 +893,6 @@
     <t>NA</t>
   </si>
   <si>
-    <t>1st</t>
-  </si>
-  <si>
-    <t>2nd</t>
-  </si>
-  <si>
-    <t>3rd</t>
-  </si>
-  <si>
-    <t>4th</t>
-  </si>
-  <si>
-    <t>5th</t>
-  </si>
-  <si>
-    <t>6th</t>
-  </si>
-  <si>
-    <t>7th</t>
-  </si>
-  <si>
-    <t>8th</t>
-  </si>
-  <si>
     <t>002527</t>
   </si>
   <si>
@@ -930,9 +906,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$]dd/mm/yyyy\ g;@"/>
-  </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1058,7 +1031,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1076,9 +1049,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1099,9 +1069,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1112,9 +1079,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1135,11 +1099,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1491,7 +1467,7 @@
     <col min="5" max="5" width="15.6640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="36" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17" style="29" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="2"/>
     <col min="10" max="10" width="29.33203125" style="2" customWidth="1"/>
     <col min="11" max="11" width="10" style="1" customWidth="1"/>
@@ -1519,34 +1495,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:79" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="16" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -1758,34 +1734,34 @@
       </c>
     </row>
     <row r="2" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I2" s="20" t="s">
+      <c r="F2" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="20" t="str">
+      <c r="J2" s="17" t="str">
         <f>IF(AI2&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI2&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI2&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI2&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI2&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -1855,34 +1831,34 @@
       <c r="AU2" s="2"/>
     </row>
     <row r="3" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I3" s="20" t="s">
+      <c r="F3" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="20" t="str">
+      <c r="J3" s="17" t="str">
         <f t="shared" ref="J3:J19" si="0">IF(AI3&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI3&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI3&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI3&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI3&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -1952,34 +1928,34 @@
       <c r="AU3" s="2"/>
     </row>
     <row r="4" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I4" s="20" t="s">
+      <c r="F4" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I4" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J4" s="20" t="str">
+      <c r="J4" s="17" t="str">
         <f>IF(AI4&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI4&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI4&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI4&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI4&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2049,34 +2025,34 @@
       <c r="AU4" s="2"/>
     </row>
     <row r="5" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I5" s="20" t="s">
+      <c r="F5" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I5" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J5" s="20" t="str">
+      <c r="J5" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2146,34 +2122,34 @@
       <c r="AU5" s="2"/>
     </row>
     <row r="6" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H6" s="21">
+      <c r="F6" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H6" s="18">
         <v>45666</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="20" t="str">
+      <c r="J6" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2243,34 +2219,34 @@
       <c r="AU6" s="2"/>
     </row>
     <row r="7" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="18">
         <v>45666</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J7" s="20" t="str">
+      <c r="J7" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2340,34 +2316,34 @@
       <c r="AU7" s="2"/>
     </row>
     <row r="8" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I8" s="20" t="s">
+      <c r="F8" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I8" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J8" s="20" t="str">
+      <c r="J8" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2437,34 +2413,34 @@
       <c r="AU8" s="2"/>
     </row>
     <row r="9" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="18">
         <v>45666</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J9" s="20" t="str">
+      <c r="J9" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2534,34 +2510,34 @@
       <c r="AU9" s="2"/>
     </row>
     <row r="10" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A10" s="28" t="s">
-        <v>290</v>
-      </c>
-      <c r="B10" s="20" t="s">
+      <c r="A10" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H10" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I10" s="20" t="s">
+      <c r="F10" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I10" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J10" s="20" t="str">
+      <c r="J10" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2631,34 +2607,34 @@
       <c r="AU10" s="2"/>
     </row>
     <row r="11" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I11" s="20" t="s">
+      <c r="F11" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I11" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J11" s="20" t="str">
+      <c r="J11" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2731,31 +2707,31 @@
       <c r="A12" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F12" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H12" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I12" s="20" t="s">
+      <c r="F12" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I12" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J12" s="20" t="str">
+      <c r="J12" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2828,29 +2804,29 @@
       <c r="A13" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20" t="s">
+      <c r="C13" s="17"/>
+      <c r="D13" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H13" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I13" s="20" t="s">
+      <c r="F13" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I13" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J13" s="20" t="str">
+      <c r="J13" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -2921,33 +2897,33 @@
     </row>
     <row r="14" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="B14" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="B14" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H14" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I14" s="20" t="s">
+      <c r="F14" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I14" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J14" s="20" t="str">
+      <c r="J14" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -3017,34 +2993,34 @@
       <c r="AU14" s="2"/>
     </row>
     <row r="15" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H15" s="7">
+      <c r="F15" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H15" s="27">
         <v>45873</v>
       </c>
-      <c r="I15" s="20" t="s">
+      <c r="I15" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J15" s="20" t="str">
+      <c r="J15" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -3114,34 +3090,34 @@
       <c r="AU15" s="2"/>
     </row>
     <row r="16" spans="1:79" x14ac:dyDescent="0.35">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H16" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I16" s="20" t="s">
+      <c r="F16" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I16" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J16" s="20" t="str">
+      <c r="J16" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -3214,31 +3190,31 @@
       <c r="A17" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H17" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I17" s="20" t="s">
+      <c r="F17" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I17" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J17" s="20" t="str">
+      <c r="J17" s="17" t="str">
         <f t="shared" si="0"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -3311,31 +3287,31 @@
       <c r="A18" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H18" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I18" s="20" t="s">
+      <c r="F18" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I18" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J18" s="20" t="str">
+      <c r="J18" s="17" t="str">
         <f t="shared" si="0"/>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -3408,31 +3384,31 @@
       <c r="A19" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H19" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I19" s="20" t="s">
+      <c r="F19" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I19" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J19" s="20" t="str">
+      <c r="J19" s="17" t="str">
         <f t="shared" si="0"/>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -3502,39 +3478,39 @@
       <c r="AU19" s="2"/>
     </row>
     <row r="20" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="D20" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="E20" s="20" t="s">
+      <c r="D20" s="17">
+        <v>1</v>
+      </c>
+      <c r="E20" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H20" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I20" s="20" t="s">
+      <c r="F20" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I20" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J20" s="20" t="s">
+      <c r="J20" s="17" t="s">
         <v>126</v>
       </c>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
-      <c r="M20" s="8"/>
+      <c r="M20" s="7"/>
       <c r="N20" s="2"/>
       <c r="O20" s="5"/>
       <c r="P20" s="2"/>
@@ -3571,34 +3547,34 @@
       <c r="AU20" s="2"/>
     </row>
     <row r="21" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="D21" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="E21" s="20" t="s">
+      <c r="D21" s="17">
+        <v>1</v>
+      </c>
+      <c r="E21" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F21" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H21" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I21" s="20" t="s">
+      <c r="F21" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I21" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="17" t="s">
         <v>130</v>
       </c>
       <c r="K21" s="5">
@@ -3607,7 +3583,7 @@
       <c r="L21" s="5">
         <v>25</v>
       </c>
-      <c r="M21" s="8">
+      <c r="M21" s="7">
         <v>20</v>
       </c>
       <c r="N21" s="2"/>
@@ -3663,31 +3639,31 @@
       <c r="A22" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="D22" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="E22" s="20" t="s">
+      <c r="D22" s="17">
+        <v>1</v>
+      </c>
+      <c r="E22" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F22" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H22" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I22" s="20" t="s">
+      <c r="F22" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I22" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J22" s="20" t="s">
+      <c r="J22" s="17" t="s">
         <v>135</v>
       </c>
       <c r="K22" s="5">
@@ -3696,7 +3672,7 @@
       <c r="L22" s="5">
         <v>30</v>
       </c>
-      <c r="M22" s="8">
+      <c r="M22" s="7">
         <v>29</v>
       </c>
       <c r="N22" s="2"/>
@@ -3749,39 +3725,39 @@
       <c r="AU22" s="2"/>
     </row>
     <row r="23" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="D23" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="E23" s="20" t="s">
+      <c r="D23" s="17">
+        <v>1</v>
+      </c>
+      <c r="E23" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H23" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I23" s="20" t="s">
+      <c r="F23" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I23" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J23" s="20" t="s">
+      <c r="J23" s="17" t="s">
         <v>126</v>
       </c>
       <c r="K23" s="5"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
       <c r="N23" s="2"/>
       <c r="O23" s="5"/>
       <c r="P23" s="2"/>
@@ -3827,29 +3803,29 @@
       <c r="A24" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="E24" s="20" t="s">
+      <c r="C24" s="17"/>
+      <c r="D24" s="17">
+        <v>1</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="27">
         <v>44596</v>
       </c>
-      <c r="I24" s="20" t="s">
+      <c r="I24" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J24" s="20" t="s">
+      <c r="J24" s="17" t="s">
         <v>135</v>
       </c>
       <c r="K24" s="5">
@@ -3858,7 +3834,7 @@
       <c r="L24" s="5">
         <v>32</v>
       </c>
-      <c r="M24" s="8">
+      <c r="M24" s="7">
         <v>38</v>
       </c>
       <c r="N24" s="2"/>
@@ -3911,34 +3887,34 @@
       <c r="AU24" s="2"/>
     </row>
     <row r="25" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="D25" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="E25" s="20" t="s">
+      <c r="D25" s="17">
+        <v>2</v>
+      </c>
+      <c r="E25" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F25" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H25" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I25" s="20" t="s">
+      <c r="F25" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I25" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J25" s="20" t="s">
+      <c r="J25" s="17" t="s">
         <v>130</v>
       </c>
       <c r="K25" s="5">
@@ -4000,34 +3976,34 @@
       <c r="AU25" s="2"/>
     </row>
     <row r="26" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="E26" s="20" t="s">
+      <c r="D26" s="17">
+        <v>2</v>
+      </c>
+      <c r="E26" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G26" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H26" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I26" s="20" t="s">
+      <c r="F26" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I26" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J26" s="20" t="s">
+      <c r="J26" s="17" t="s">
         <v>147</v>
       </c>
       <c r="K26" s="5">
@@ -4089,34 +4065,34 @@
       <c r="AU26" s="2"/>
     </row>
     <row r="27" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="D27" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="E27" s="20" t="s">
+      <c r="D27" s="17">
+        <v>2</v>
+      </c>
+      <c r="E27" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F27" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H27" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I27" s="20" t="s">
+      <c r="F27" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I27" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J27" s="20" t="s">
+      <c r="J27" s="17" t="s">
         <v>147</v>
       </c>
       <c r="K27" s="5">
@@ -4178,34 +4154,34 @@
       <c r="AU27" s="2"/>
     </row>
     <row r="28" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D28" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="E28" s="20" t="s">
+      <c r="D28" s="17">
+        <v>2</v>
+      </c>
+      <c r="E28" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H28" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I28" s="20" t="s">
+      <c r="F28" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I28" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J28" s="20" t="s">
+      <c r="J28" s="17" t="s">
         <v>130</v>
       </c>
       <c r="K28" s="5">
@@ -4267,34 +4243,34 @@
       <c r="AU28" s="2"/>
     </row>
     <row r="29" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="B29" s="20" t="s">
+      <c r="B29" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D29" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="E29" s="20" t="s">
+      <c r="D29" s="17">
+        <v>2</v>
+      </c>
+      <c r="E29" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F29" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G29" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H29" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I29" s="20" t="s">
+      <c r="F29" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H29" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I29" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J29" s="20" t="s">
+      <c r="J29" s="17" t="s">
         <v>157</v>
       </c>
       <c r="K29" s="5">
@@ -4356,34 +4332,34 @@
       <c r="AU29" s="2"/>
     </row>
     <row r="30" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="D30" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="E30" s="20" t="s">
+      <c r="D30" s="17">
+        <v>2</v>
+      </c>
+      <c r="E30" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="G30" s="22" t="s">
+      <c r="G30" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="H30" s="23">
+      <c r="H30" s="20">
         <v>45720</v>
       </c>
-      <c r="I30" s="20" t="s">
+      <c r="I30" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J30" s="20" t="s">
+      <c r="J30" s="17" t="s">
         <v>157</v>
       </c>
       <c r="K30" s="5">
@@ -4445,34 +4421,34 @@
       <c r="AU30" s="2"/>
     </row>
     <row r="31" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D31" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="E31" s="20" t="s">
+      <c r="D31" s="17">
+        <v>2</v>
+      </c>
+      <c r="E31" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F31" s="22" t="s">
+      <c r="F31" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="G31" s="22" t="s">
+      <c r="G31" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="H31" s="23">
+      <c r="H31" s="20">
         <v>44385</v>
       </c>
-      <c r="I31" s="20" t="s">
+      <c r="I31" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J31" s="20" t="s">
+      <c r="J31" s="17" t="s">
         <v>147</v>
       </c>
       <c r="K31" s="5">
@@ -4534,34 +4510,34 @@
       <c r="AU31" s="2"/>
     </row>
     <row r="32" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="D32" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="E32" s="20" t="s">
+      <c r="D32" s="17">
+        <v>2</v>
+      </c>
+      <c r="E32" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F32" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G32" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H32" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I32" s="20" t="s">
+      <c r="F32" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H32" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I32" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J32" s="20" t="s">
+      <c r="J32" s="17" t="s">
         <v>126</v>
       </c>
       <c r="K32" s="5">
@@ -4623,34 +4599,34 @@
       <c r="AU32" s="2"/>
     </row>
     <row r="33" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="B33" s="20" t="s">
+      <c r="B33" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="C33" s="20" t="s">
+      <c r="C33" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="D33" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="E33" s="20" t="s">
+      <c r="D33" s="17">
+        <v>3</v>
+      </c>
+      <c r="E33" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F33" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G33" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H33" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I33" s="20" t="s">
+      <c r="F33" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H33" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I33" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J33" s="20" t="str">
+      <c r="J33" s="17" t="str">
         <f>IF(AI33&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI33&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI33&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI33&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI33&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -4716,34 +4692,34 @@
       <c r="AU33" s="2"/>
     </row>
     <row r="34" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="D34" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="E34" s="20" t="s">
+      <c r="D34" s="17">
+        <v>3</v>
+      </c>
+      <c r="E34" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="G34" s="22" t="s">
+      <c r="G34" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="H34" s="25" t="s">
+      <c r="H34" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="I34" s="20" t="s">
+      <c r="I34" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J34" s="20" t="str">
+      <c r="J34" s="17" t="str">
         <f t="shared" ref="J34:J35" si="4">IF(AI34&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI34&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI34&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI34&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI34&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -4809,34 +4785,34 @@
       <c r="AU34" s="2"/>
     </row>
     <row r="35" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="B35" s="20" t="s">
+      <c r="B35" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="C35" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="E35" s="20" t="s">
+      <c r="D35" s="17">
+        <v>3</v>
+      </c>
+      <c r="E35" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F35" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H35" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I35" s="20" t="s">
+      <c r="F35" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H35" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I35" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J35" s="20" t="str">
+      <c r="J35" s="17" t="str">
         <f t="shared" si="4"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -4902,34 +4878,34 @@
       <c r="AU35" s="2"/>
     </row>
     <row r="36" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="C36" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="D36" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="E36" s="20" t="s">
+      <c r="D36" s="17">
+        <v>4</v>
+      </c>
+      <c r="E36" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F36" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G36" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H36" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I36" s="20" t="s">
+      <c r="F36" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G36" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H36" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I36" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J36" s="20" t="str">
+      <c r="J36" s="17" t="str">
         <f>IF(AL36&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL36&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL36&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL36&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL36&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -4997,34 +4973,34 @@
       <c r="AU36" s="2"/>
     </row>
     <row r="37" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A37" s="20" t="s">
+      <c r="A37" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="B37" s="20" t="s">
+      <c r="B37" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="D37" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="E37" s="20" t="s">
+      <c r="D37" s="17">
+        <v>4</v>
+      </c>
+      <c r="E37" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F37" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G37" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H37" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I37" s="20" t="s">
+      <c r="F37" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H37" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I37" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J37" s="20" t="str">
+      <c r="J37" s="17" t="str">
         <f t="shared" ref="J37:J40" si="8">IF(AL37&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL37&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL37&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL37&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL37&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -5092,34 +5068,34 @@
       <c r="AU37" s="2"/>
     </row>
     <row r="38" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="C38" s="20" t="s">
+      <c r="C38" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D38" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="E38" s="20" t="s">
+      <c r="D38" s="17">
+        <v>4</v>
+      </c>
+      <c r="E38" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F38" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G38" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H38" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I38" s="20" t="s">
+      <c r="F38" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G38" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I38" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J38" s="20" t="str">
+      <c r="J38" s="17" t="str">
         <f t="shared" si="8"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -5190,31 +5166,31 @@
       <c r="A39" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="E39" s="20" t="s">
+      <c r="D39" s="17">
+        <v>4</v>
+      </c>
+      <c r="E39" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F39" s="25" t="s">
+      <c r="F39" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="G39" s="25" t="s">
+      <c r="G39" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="H39" s="23">
+      <c r="H39" s="20">
         <v>45386</v>
       </c>
-      <c r="I39" s="20" t="s">
+      <c r="I39" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J39" s="20" t="str">
+      <c r="J39" s="17" t="str">
         <f t="shared" si="8"/>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -5285,31 +5261,31 @@
       <c r="A40" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="D40" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="E40" s="20" t="s">
+      <c r="D40" s="17">
+        <v>4</v>
+      </c>
+      <c r="E40" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F40" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G40" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H40" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I40" s="20" t="s">
+      <c r="F40" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G40" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I40" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J40" s="20" t="str">
+      <c r="J40" s="17" t="str">
         <f t="shared" si="8"/>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -5380,31 +5356,31 @@
       <c r="A41" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="D41" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="E41" s="20" t="s">
+      <c r="D41" s="17">
+        <v>5</v>
+      </c>
+      <c r="E41" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F41" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="G41" s="25" t="s">
+      <c r="G41" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="H41" s="23">
+      <c r="H41" s="20">
         <v>45386</v>
       </c>
-      <c r="I41" s="20" t="s">
+      <c r="I41" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J41" s="20" t="str">
+      <c r="J41" s="17" t="str">
         <f>IF(AL41&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL41&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL41&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL41&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL41&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -5475,31 +5451,31 @@
       <c r="A42" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="D42" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="E42" s="20" t="s">
+      <c r="D42" s="17">
+        <v>5</v>
+      </c>
+      <c r="E42" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F42" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G42" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H42" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I42" s="20" t="s">
+      <c r="F42" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G42" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H42" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I42" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J42" s="20" t="str">
+      <c r="J42" s="17" t="str">
         <f t="shared" ref="J42:J47" si="12">IF(AL42&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL42&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL42&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL42&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL42&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -5570,31 +5546,31 @@
       <c r="A43" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D43" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="E43" s="20" t="s">
+      <c r="D43" s="17">
+        <v>5</v>
+      </c>
+      <c r="E43" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F43" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G43" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H43" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I43" s="20" t="s">
+      <c r="F43" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H43" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I43" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J43" s="20" t="str">
+      <c r="J43" s="17" t="str">
         <f t="shared" si="12"/>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -5665,31 +5641,31 @@
       <c r="A44" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="D44" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="E44" s="20" t="s">
+      <c r="D44" s="17">
+        <v>5</v>
+      </c>
+      <c r="E44" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F44" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G44" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H44" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I44" s="20" t="s">
+      <c r="F44" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H44" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I44" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J44" s="20" t="str">
+      <c r="J44" s="17" t="str">
         <f t="shared" si="12"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -5760,31 +5736,31 @@
       <c r="A45" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="D45" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="E45" s="20" t="s">
+      <c r="D45" s="17">
+        <v>5</v>
+      </c>
+      <c r="E45" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F45" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G45" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H45" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I45" s="20" t="s">
+      <c r="F45" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G45" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H45" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I45" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J45" s="20" t="str">
+      <c r="J45" s="17" t="str">
         <f t="shared" si="12"/>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -5855,31 +5831,31 @@
       <c r="A46" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="D46" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="E46" s="20" t="s">
+      <c r="D46" s="17">
+        <v>5</v>
+      </c>
+      <c r="E46" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F46" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G46" s="11" t="s">
+      <c r="F46" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G46" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="H46" s="25" t="s">
+      <c r="H46" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="I46" s="20" t="s">
+      <c r="I46" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J46" s="20" t="str">
+      <c r="J46" s="17" t="str">
         <f t="shared" si="12"/>
         <v>Don't lose heart! With extra hard work, you can improve.</v>
       </c>
@@ -5950,31 +5926,31 @@
       <c r="A47" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="D47" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="E47" s="20" t="s">
+      <c r="D47" s="17">
+        <v>5</v>
+      </c>
+      <c r="E47" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F47" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G47" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H47" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I47" s="20" t="s">
+      <c r="F47" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H47" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I47" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J47" s="20" t="str">
+      <c r="J47" s="17" t="str">
         <f t="shared" si="12"/>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -6045,31 +6021,31 @@
       <c r="A48" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="D48" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="E48" s="20" t="s">
+      <c r="D48" s="17">
+        <v>6</v>
+      </c>
+      <c r="E48" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F48" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G48" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H48" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I48" s="20" t="s">
+      <c r="F48" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G48" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H48" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I48" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J48" s="20" t="str">
+      <c r="J48" s="17" t="str">
         <f>IF(AM48&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AM48&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AM48&gt;=60, "Well done! You have great potential to achieve even more.", IF(AM48&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AM48&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Don't lose heart! With extra hard work, you can improve.</v>
       </c>
@@ -6140,31 +6116,31 @@
       <c r="A49" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="D49" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="E49" s="20" t="s">
+      <c r="D49" s="17">
+        <v>6</v>
+      </c>
+      <c r="E49" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F49" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G49" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H49" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I49" s="20" t="s">
+      <c r="F49" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G49" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H49" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I49" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J49" s="20" t="str">
+      <c r="J49" s="17" t="str">
         <f t="shared" ref="J49:J53" si="16">IF(AM49&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AM49&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AM49&gt;=60, "Well done! You have great potential to achieve even more.", IF(AM49&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AM49&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -6235,31 +6211,31 @@
       <c r="A50" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="D50" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="E50" s="20" t="s">
+      <c r="D50" s="17">
+        <v>6</v>
+      </c>
+      <c r="E50" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F50" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G50" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H50" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I50" s="20" t="s">
+      <c r="F50" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G50" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I50" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J50" s="20" t="str">
+      <c r="J50" s="17" t="str">
         <f t="shared" si="16"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -6330,31 +6306,31 @@
       <c r="A51" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="D51" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="E51" s="20" t="s">
+      <c r="D51" s="17">
+        <v>6</v>
+      </c>
+      <c r="E51" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F51" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G51" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H51" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I51" s="20" t="s">
+      <c r="F51" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G51" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H51" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I51" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J51" s="20" t="str">
+      <c r="J51" s="17" t="str">
         <f t="shared" si="16"/>
         <v>Don't lose heart! With extra hard work, you can improve.</v>
       </c>
@@ -6422,34 +6398,34 @@
       <c r="AU51" s="2"/>
     </row>
     <row r="52" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A52" s="12" t="s">
+      <c r="A52" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B52" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="D52" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="E52" s="20" t="s">
+      <c r="D52" s="17">
+        <v>6</v>
+      </c>
+      <c r="E52" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F52" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G52" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H52" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I52" s="20" t="s">
+      <c r="F52" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G52" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H52" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I52" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J52" s="20" t="str">
+      <c r="J52" s="17" t="str">
         <f t="shared" si="16"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -6520,31 +6496,31 @@
       <c r="A53" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="D53" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="E53" s="20" t="s">
+      <c r="D53" s="17">
+        <v>6</v>
+      </c>
+      <c r="E53" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F53" s="13" t="s">
+      <c r="F53" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="G53" s="10" t="s">
+      <c r="G53" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="H53" s="14">
+      <c r="H53" s="28">
         <v>45750</v>
       </c>
-      <c r="I53" s="20" t="s">
+      <c r="I53" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J53" s="20" t="str">
+      <c r="J53" s="17" t="str">
         <f t="shared" si="16"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -6615,31 +6591,31 @@
       <c r="A54" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C54" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="D54" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="E54" s="20" t="s">
+      <c r="D54" s="17">
+        <v>7</v>
+      </c>
+      <c r="E54" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F54" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G54" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H54" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I54" s="20" t="s">
+      <c r="F54" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G54" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H54" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I54" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J54" s="20" t="str">
+      <c r="J54" s="17" t="str">
         <f>IF(AM54&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AM54&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AM54&gt;=60, "Well done! You have great potential to achieve even more.", IF(AM54&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AM54&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Impressive work! Your dedication is truly paying off.</v>
       </c>
@@ -6710,31 +6686,31 @@
       <c r="A55" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C55" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="D55" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="E55" s="20" t="s">
+      <c r="D55" s="17">
+        <v>7</v>
+      </c>
+      <c r="E55" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F55" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G55" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H55" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I55" s="20" t="s">
+      <c r="F55" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G55" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H55" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I55" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J55" s="20" t="str">
+      <c r="J55" s="17" t="str">
         <f t="shared" ref="J55:J59" si="20">IF(AM55&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AM55&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AM55&gt;=60, "Well done! You have great potential to achieve even more.", IF(AM55&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AM55&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -6805,31 +6781,31 @@
       <c r="A56" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="B56" s="16" t="s">
+      <c r="B56" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C56" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="D56" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="E56" s="20" t="s">
+      <c r="D56" s="17">
+        <v>7</v>
+      </c>
+      <c r="E56" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G56" s="11" t="s">
+      <c r="F56" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G56" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="H56" s="20" t="s">
+      <c r="H56" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="I56" s="20" t="s">
+      <c r="I56" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J56" s="20" t="str">
+      <c r="J56" s="17" t="str">
         <f t="shared" si="20"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -6900,31 +6876,31 @@
       <c r="A57" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="B57" s="16" t="s">
+      <c r="B57" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C57" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="D57" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="E57" s="20" t="s">
+      <c r="D57" s="17">
+        <v>7</v>
+      </c>
+      <c r="E57" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F57" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G57" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H57" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I57" s="20" t="s">
+      <c r="F57" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G57" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I57" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J57" s="20" t="str">
+      <c r="J57" s="17" t="str">
         <f t="shared" si="20"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -6995,31 +6971,31 @@
       <c r="A58" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C58" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="D58" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="E58" s="20" t="s">
+      <c r="D58" s="17">
+        <v>7</v>
+      </c>
+      <c r="E58" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F58" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G58" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H58" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I58" s="20" t="s">
+      <c r="F58" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G58" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H58" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I58" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J58" s="20" t="str">
+      <c r="J58" s="17" t="str">
         <f t="shared" si="20"/>
         <v>Outstanding achievement! You are a shining star of our class.</v>
       </c>
@@ -7090,31 +7066,31 @@
       <c r="A59" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="C59" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="D59" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="E59" s="20" t="s">
+      <c r="D59" s="17">
+        <v>7</v>
+      </c>
+      <c r="E59" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F59" s="20" t="s">
+      <c r="F59" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="G59" s="20" t="s">
+      <c r="G59" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="H59" s="21">
+      <c r="H59" s="18">
         <v>45327</v>
       </c>
-      <c r="I59" s="20" t="s">
+      <c r="I59" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J59" s="20" t="str">
+      <c r="J59" s="17" t="str">
         <f t="shared" si="20"/>
         <v>Impressive work! Your dedication is truly paying off.</v>
       </c>
@@ -7185,31 +7161,31 @@
       <c r="A60" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="B60" s="16" t="s">
+      <c r="B60" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="C60" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="D60" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="E60" s="20" t="s">
+      <c r="D60" s="17">
+        <v>8</v>
+      </c>
+      <c r="E60" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F60" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G60" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H60" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I60" s="20" t="s">
+      <c r="F60" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G60" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H60" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I60" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J60" s="20" t="str">
+      <c r="J60" s="17" t="str">
         <f>IF(AN60&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AN60&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AN60&gt;=60, "Well done! You have great potential to achieve even more.", IF(AN60&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AN60&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
@@ -7280,31 +7256,31 @@
       <c r="A61" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C61" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="D61" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="E61" s="20" t="s">
+      <c r="D61" s="17">
+        <v>8</v>
+      </c>
+      <c r="E61" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F61" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G61" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H61" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I61" s="20" t="s">
+      <c r="F61" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G61" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H61" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I61" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J61" s="20" t="str">
+      <c r="J61" s="17" t="str">
         <f t="shared" ref="J61:J66" si="24">IF(AN61&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AN61&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AN61&gt;=60, "Well done! You have great potential to achieve even more.", IF(AN61&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AN61&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -7375,31 +7351,31 @@
       <c r="A62" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="B62" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="C62" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="D62" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="E62" s="20" t="s">
+      <c r="D62" s="17">
+        <v>8</v>
+      </c>
+      <c r="E62" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F62" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G62" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H62" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I62" s="20" t="s">
+      <c r="F62" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G62" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H62" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I62" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J62" s="20" t="str">
+      <c r="J62" s="17" t="str">
         <f t="shared" si="24"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -7470,31 +7446,31 @@
       <c r="A63" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B63" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="C63" s="16" t="s">
+      <c r="C63" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="D63" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="E63" s="20" t="s">
+      <c r="D63" s="17">
+        <v>8</v>
+      </c>
+      <c r="E63" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F63" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G63" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H63" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I63" s="20" t="s">
+      <c r="F63" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G63" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H63" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I63" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J63" s="20" t="str">
+      <c r="J63" s="17" t="str">
         <f t="shared" si="24"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -7565,31 +7541,31 @@
       <c r="A64" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B64" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="C64" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="D64" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="E64" s="20" t="s">
+      <c r="D64" s="17">
+        <v>8</v>
+      </c>
+      <c r="E64" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F64" s="15" t="s">
+      <c r="F64" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="G64" s="10" t="s">
+      <c r="G64" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="H64" s="14">
+      <c r="H64" s="28">
         <v>45750</v>
       </c>
-      <c r="I64" s="20" t="s">
+      <c r="I64" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J64" s="20" t="str">
+      <c r="J64" s="17" t="str">
         <f t="shared" si="24"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -7660,31 +7636,31 @@
       <c r="A65" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="C65" s="16" t="s">
+      <c r="C65" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="D65" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="E65" s="20" t="s">
+      <c r="D65" s="17">
+        <v>8</v>
+      </c>
+      <c r="E65" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F65" s="10" t="s">
+      <c r="F65" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="G65" s="10" t="s">
+      <c r="G65" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="H65" s="20" t="s">
+      <c r="H65" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="I65" s="20" t="s">
+      <c r="I65" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J65" s="20" t="str">
+      <c r="J65" s="17" t="str">
         <f t="shared" si="24"/>
         <v>Impressive work! Your dedication is truly paying off.</v>
       </c>
@@ -7755,31 +7731,31 @@
       <c r="A66" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="B66" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="D66" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="E66" s="20" t="s">
+      <c r="D66" s="17">
+        <v>8</v>
+      </c>
+      <c r="E66" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F66" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G66" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H66" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I66" s="20" t="s">
+      <c r="F66" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G66" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H66" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I66" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J66" s="20" t="str">
+      <c r="J66" s="17" t="str">
         <f t="shared" si="24"/>
         <v>Good effort! A little more focus will lead to better results.</v>
       </c>
@@ -7850,31 +7826,31 @@
       <c r="A67" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="B67" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="C67" s="16" t="s">
+      <c r="C67" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="D67" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="E67" s="20" t="s">
+      <c r="D67" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="E67" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F67" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G67" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H67" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I67" s="20" t="s">
+      <c r="F67" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G67" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H67" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I67" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J67" s="20" t="str">
+      <c r="J67" s="17" t="str">
         <f>IF(AL67&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL67&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL67&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL67&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL67&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>We believe in you! Let's work together for a strong comeback.</v>
       </c>
@@ -7939,31 +7915,31 @@
       <c r="A68" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="C68" s="16" t="s">
+      <c r="C68" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="D68" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="E68" s="20" t="s">
+      <c r="D68" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="E68" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F68" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G68" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="H68" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I68" s="20" t="s">
+      <c r="F68" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G68" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H68" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I68" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J68" s="20" t="str">
+      <c r="J68" s="17" t="str">
         <f t="shared" ref="J68" si="28">IF(AL68&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AL68&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AL68&gt;=60, "Well done! You have great potential to achieve even more.", IF(AL68&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AL68&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Impressive work! Your dedication is truly paying off.</v>
       </c>
@@ -8113,10 +8089,10 @@
       <c r="J5" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="27" t="s">
+      <c r="L5" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="M5" s="27"/>
+      <c r="M5" s="25"/>
       <c r="N5" t="s">
         <v>11</v>
       </c>
@@ -8137,10 +8113,10 @@
       <c r="J6" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="27" t="s">
+      <c r="L6" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="27"/>
+      <c r="M6" s="25"/>
       <c r="N6" t="s">
         <v>50</v>
       </c>
@@ -8161,10 +8137,10 @@
       <c r="J7" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="M7" s="27"/>
+      <c r="M7" s="25"/>
       <c r="N7" t="s">
         <v>48</v>
       </c>
@@ -8185,10 +8161,10 @@
       <c r="J8" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="27" t="s">
+      <c r="L8" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="M8" s="27"/>
+      <c r="M8" s="25"/>
       <c r="N8" t="s">
         <v>51</v>
       </c>
@@ -8209,10 +8185,10 @@
       <c r="J9" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="27" t="s">
+      <c r="L9" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="27"/>
+      <c r="M9" s="25"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
@@ -8230,10 +8206,10 @@
       <c r="J10" t="s">
         <v>27</v>
       </c>
-      <c r="L10" s="27" t="s">
+      <c r="L10" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="M10" s="27"/>
+      <c r="M10" s="25"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
@@ -8251,10 +8227,10 @@
       <c r="J11" t="s">
         <v>26</v>
       </c>
-      <c r="L11" s="27" t="s">
+      <c r="L11" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="27"/>
+      <c r="M11" s="25"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="D12" t="s">
@@ -8263,10 +8239,10 @@
       <c r="F12" t="s">
         <v>48</v>
       </c>
-      <c r="L12" s="27" t="s">
+      <c r="L12" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="M12" s="27"/>
+      <c r="M12" s="25"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="L13" t="s">

--- a/data/class.xlsx
+++ b/data/class.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fast Computer\OneDrive\Desktop\folder\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/74b89d8f5a3cedb0/Desktop/folder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55EF55B6-712C-4489-BD71-CD1C9CE25803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{55EF55B6-712C-4489-BD71-CD1C9CE25803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04FB159F-C0B9-4F8C-AEA5-C0F126C3E776}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="302">
   <si>
     <t>Roll No</t>
   </si>
@@ -901,11 +901,68 @@
   <si>
     <t>8 (Arts Group)</t>
   </si>
+  <si>
+    <t>002529</t>
+  </si>
+  <si>
+    <t>Noor Fatima</t>
+  </si>
+  <si>
+    <t>Tehfeez-ul-Quran</t>
+  </si>
+  <si>
+    <t>002530</t>
+  </si>
+  <si>
+    <t>Ayesha Saddiqa</t>
+  </si>
+  <si>
+    <t>002416</t>
+  </si>
+  <si>
+    <t>Azan  Ilyas</t>
+  </si>
+  <si>
+    <t>Muhammad Ilyas</t>
+  </si>
+  <si>
+    <t>002417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hasam Ilyas  </t>
+  </si>
+  <si>
+    <t>002422</t>
+  </si>
+  <si>
+    <t>Abdullah Imran</t>
+  </si>
+  <si>
+    <t>Imran Khan</t>
+  </si>
+  <si>
+    <t>002411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniyal Abbasi     </t>
+  </si>
+  <si>
+    <t>Taimoor Ali Abbasi</t>
+  </si>
+  <si>
+    <t>2024-010</t>
+  </si>
+  <si>
+    <t>Salman Khalid</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$]dd/mm/yyyy\ g;@"/>
+  </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1031,7 +1088,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1102,10 +1159,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1117,6 +1170,18 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1457,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CA68"/>
+  <dimension ref="A1:CA75"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="2"/>
@@ -1467,7 +1532,7 @@
     <col min="5" max="5" width="15.6640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="36" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17" style="29" customWidth="1"/>
+    <col min="8" max="8" width="17" style="27" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="2"/>
     <col min="10" max="10" width="29.33203125" style="2" customWidth="1"/>
     <col min="11" max="11" width="10" style="1" customWidth="1"/>
@@ -1516,7 +1581,7 @@
       <c r="G1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="24" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="16" t="s">
@@ -3014,7 +3079,7 @@
       <c r="G15" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="25">
         <v>45873</v>
       </c>
       <c r="I15" s="17" t="s">
@@ -3756,8 +3821,8 @@
         <v>126</v>
       </c>
       <c r="K23" s="5"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
       <c r="N23" s="2"/>
       <c r="O23" s="5"/>
       <c r="P23" s="2"/>
@@ -3819,7 +3884,7 @@
       <c r="G24" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="H24" s="27">
+      <c r="H24" s="25">
         <v>44596</v>
       </c>
       <c r="I24" s="17" t="s">
@@ -6514,7 +6579,7 @@
       <c r="G53" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="H53" s="28">
+      <c r="H53" s="26">
         <v>45750</v>
       </c>
       <c r="I53" s="17" t="s">
@@ -7559,7 +7624,7 @@
       <c r="G64" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="H64" s="28">
+      <c r="H64" s="26">
         <v>45750</v>
       </c>
       <c r="I64" s="17" t="s">
@@ -8005,6 +8070,327 @@
       <c r="AS68" s="2"/>
       <c r="AT68" s="2"/>
       <c r="AU68" s="2"/>
+    </row>
+    <row r="69" spans="1:47" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B69" t="s">
+        <v>285</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H69" s="30"/>
+      <c r="I69" t="s">
+        <v>79</v>
+      </c>
+      <c r="J69" t="str">
+        <f>IF(AI69&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI69&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI69&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI69&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI69&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
+        <v>Well done! You have great potential to achieve even more.</v>
+      </c>
+      <c r="K69" s="5">
+        <v>49.5</v>
+      </c>
+      <c r="L69" s="5">
+        <v>26</v>
+      </c>
+      <c r="M69" s="5">
+        <v>71.5</v>
+      </c>
+      <c r="U69" s="31"/>
+      <c r="AG69" s="5">
+        <v>65</v>
+      </c>
+      <c r="AH69" s="2">
+        <f>SUM(K69:AG69)</f>
+        <v>212</v>
+      </c>
+      <c r="AI69" s="2">
+        <f>(AH69/325)*100</f>
+        <v>65.230769230769226</v>
+      </c>
+      <c r="AJ69" s="2" t="str">
+        <f>IF(AI69&gt;=80, "A+", IF(AI69&gt;=70, "A", IF(AI69&gt;=60, "B", IF(AI69&gt;=50, "C", IF(AI69&gt;=40, "D", "FAIL")))))</f>
+        <v>B</v>
+      </c>
+    </row>
+    <row r="70" spans="1:47" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B70" t="s">
+        <v>288</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H70" s="30"/>
+      <c r="I70" t="s">
+        <v>79</v>
+      </c>
+      <c r="J70" t="str">
+        <f>IF(AI70&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI70&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI70&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI70&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI70&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
+        <v>Well done! You have great potential to achieve even more.</v>
+      </c>
+      <c r="K70" s="5">
+        <v>30</v>
+      </c>
+      <c r="L70" s="5">
+        <v>51</v>
+      </c>
+      <c r="M70" s="5">
+        <v>47</v>
+      </c>
+      <c r="U70" s="31"/>
+      <c r="AG70" s="5">
+        <v>86</v>
+      </c>
+      <c r="AH70" s="2">
+        <f t="shared" ref="AH70:AH75" si="29">SUM(K70:AG70)</f>
+        <v>214</v>
+      </c>
+      <c r="AI70" s="2">
+        <f t="shared" ref="AI70:AI75" si="30">(AH70/325)*100</f>
+        <v>65.84615384615384</v>
+      </c>
+      <c r="AJ70" s="2" t="str">
+        <f t="shared" ref="AJ70:AJ75" si="31">IF(AI70&gt;=80, "A+", IF(AI70&gt;=70, "A", IF(AI70&gt;=60, "B", IF(AI70&gt;=50, "C", IF(AI70&gt;=40, "D", "FAIL")))))</f>
+        <v>B</v>
+      </c>
+    </row>
+    <row r="71" spans="1:47" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B71" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="C71" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H71" s="30"/>
+      <c r="I71" t="s">
+        <v>79</v>
+      </c>
+      <c r="J71" t="str">
+        <f t="shared" ref="J71:J74" si="32">IF(AI71&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI71&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI71&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI71&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI71&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
+        <v>Well done! You have great potential to achieve even more.</v>
+      </c>
+      <c r="K71" s="5">
+        <v>44</v>
+      </c>
+      <c r="L71" s="5">
+        <v>49</v>
+      </c>
+      <c r="M71" s="5">
+        <v>36</v>
+      </c>
+      <c r="U71" s="31"/>
+      <c r="AG71" s="5">
+        <v>81</v>
+      </c>
+      <c r="AH71" s="2">
+        <f t="shared" si="29"/>
+        <v>210</v>
+      </c>
+      <c r="AI71" s="2">
+        <f t="shared" si="30"/>
+        <v>64.615384615384613</v>
+      </c>
+      <c r="AJ71" s="2" t="str">
+        <f t="shared" si="31"/>
+        <v>B</v>
+      </c>
+    </row>
+    <row r="72" spans="1:47" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="B72" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="C72" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H72" s="30"/>
+      <c r="I72" t="s">
+        <v>79</v>
+      </c>
+      <c r="J72" t="str">
+        <f t="shared" si="32"/>
+        <v>Good effort! A little more focus will lead to better results.</v>
+      </c>
+      <c r="K72" s="5">
+        <v>25</v>
+      </c>
+      <c r="L72" s="5">
+        <v>30</v>
+      </c>
+      <c r="M72" s="5">
+        <v>39</v>
+      </c>
+      <c r="U72" s="31"/>
+      <c r="AG72" s="5">
+        <v>79</v>
+      </c>
+      <c r="AH72" s="2">
+        <f t="shared" si="29"/>
+        <v>173</v>
+      </c>
+      <c r="AI72" s="2">
+        <f t="shared" si="30"/>
+        <v>53.230769230769226</v>
+      </c>
+      <c r="AJ72" s="2" t="str">
+        <f t="shared" si="31"/>
+        <v>C</v>
+      </c>
+    </row>
+    <row r="73" spans="1:47" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B73" t="s">
+        <v>295</v>
+      </c>
+      <c r="C73" t="s">
+        <v>296</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H73" s="30"/>
+      <c r="I73" t="s">
+        <v>79</v>
+      </c>
+      <c r="J73" t="str">
+        <f t="shared" si="32"/>
+        <v>Don't lose heart! With extra hard work, you can improve.</v>
+      </c>
+      <c r="K73" s="5">
+        <v>22</v>
+      </c>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5">
+        <v>40</v>
+      </c>
+      <c r="U73" s="31"/>
+      <c r="AG73" s="5">
+        <v>83</v>
+      </c>
+      <c r="AH73" s="2">
+        <f t="shared" si="29"/>
+        <v>145</v>
+      </c>
+      <c r="AI73" s="2">
+        <f t="shared" si="30"/>
+        <v>44.61538461538462</v>
+      </c>
+      <c r="AJ73" s="2" t="str">
+        <f t="shared" si="31"/>
+        <v>D</v>
+      </c>
+    </row>
+    <row r="74" spans="1:47" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B74" s="32" t="s">
+        <v>298</v>
+      </c>
+      <c r="C74" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="H74" s="33">
+        <v>43834</v>
+      </c>
+      <c r="I74" t="s">
+        <v>79</v>
+      </c>
+      <c r="J74" t="str">
+        <f t="shared" si="32"/>
+        <v>Well done! You have great potential to achieve even more.</v>
+      </c>
+      <c r="K74" s="5">
+        <v>35</v>
+      </c>
+      <c r="L74" s="5">
+        <v>28</v>
+      </c>
+      <c r="M74" s="5">
+        <v>48</v>
+      </c>
+      <c r="U74" s="31"/>
+      <c r="AG74" s="5">
+        <v>88</v>
+      </c>
+      <c r="AH74" s="2">
+        <f t="shared" si="29"/>
+        <v>199</v>
+      </c>
+      <c r="AI74" s="2">
+        <f t="shared" si="30"/>
+        <v>61.230769230769234</v>
+      </c>
+      <c r="AJ74" s="2" t="str">
+        <f t="shared" si="31"/>
+        <v>B</v>
+      </c>
+    </row>
+    <row r="75" spans="1:47" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D75" s="2"/>
+      <c r="H75" s="30"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="5"/>
+      <c r="M75" s="5"/>
+      <c r="U75" s="31"/>
+      <c r="AG75" s="5"/>
+      <c r="AH75" s="2">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AI75" s="2">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="2" t="str">
+        <f t="shared" si="31"/>
+        <v>FAIL</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:CA68" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -8089,10 +8475,10 @@
       <c r="J5" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="25" t="s">
+      <c r="L5" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="M5" s="25"/>
+      <c r="M5" s="29"/>
       <c r="N5" t="s">
         <v>11</v>
       </c>
@@ -8113,10 +8499,10 @@
       <c r="J6" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="25" t="s">
+      <c r="L6" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="25"/>
+      <c r="M6" s="29"/>
       <c r="N6" t="s">
         <v>50</v>
       </c>
@@ -8137,10 +8523,10 @@
       <c r="J7" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="L7" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="M7" s="25"/>
+      <c r="M7" s="29"/>
       <c r="N7" t="s">
         <v>48</v>
       </c>
@@ -8161,10 +8547,10 @@
       <c r="J8" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="25" t="s">
+      <c r="L8" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="M8" s="25"/>
+      <c r="M8" s="29"/>
       <c r="N8" t="s">
         <v>51</v>
       </c>
@@ -8185,10 +8571,10 @@
       <c r="J9" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="25" t="s">
+      <c r="L9" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="25"/>
+      <c r="M9" s="29"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
@@ -8206,10 +8592,10 @@
       <c r="J10" t="s">
         <v>27</v>
       </c>
-      <c r="L10" s="25" t="s">
+      <c r="L10" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="M10" s="25"/>
+      <c r="M10" s="29"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
@@ -8227,10 +8613,10 @@
       <c r="J11" t="s">
         <v>26</v>
       </c>
-      <c r="L11" s="25" t="s">
+      <c r="L11" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="25"/>
+      <c r="M11" s="29"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="D12" t="s">
@@ -8239,10 +8625,10 @@
       <c r="F12" t="s">
         <v>48</v>
       </c>
-      <c r="L12" s="25" t="s">
+      <c r="L12" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="M12" s="25"/>
+      <c r="M12" s="29"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="L13" t="s">

--- a/data/class.xlsx
+++ b/data/class.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/74b89d8f5a3cedb0/Desktop/folder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_F6A1F43F91D74A179400985AF493EAA9998EB2D8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3F8D849-C84D-4701-90DF-B994CAD93C4D}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_F6A1F43F91D74A179400985AF493EAA9998EB2D8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2626C061-BA47-469E-91B8-CA6A0D5D353E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1016,6 +1016,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6285,7 +6289,7 @@
         <v>44</v>
       </c>
       <c r="K53">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="L53">
         <v>54</v>
@@ -8231,7 +8235,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CJ21 A74:CJ75 A72:E72 K72:CJ72 A70:E71 A69:E69 K69:CJ69 A68:E68 G68:CJ68 A73:E73 I73:K73 I72 I70:CJ71 I69 A23:CJ67 A22:J22 L22:CJ22 M73:CJ73" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CJ21 A74:CJ75 A72:E72 K72:CJ72 A70:E71 A69:E69 K69:CJ69 A68:E68 G68:CJ68 A73:E73 I73:K73 I72 I70:CJ71 I69 A23:CJ52 A22:J22 L22:CJ22 M73:CJ73 A54:CJ67 A53:J53 L53:CJ53" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/class.xlsx
+++ b/data/class.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/74b89d8f5a3cedb0/Desktop/folder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_F6A1F43F91D74A179400985AF493EAA9998EB2D8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2626C061-BA47-469E-91B8-CA6A0D5D353E}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_F6A1F43F91D74A179400985AF493EAA9998EB2D8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB3B8485-BAA1-4E37-8CB1-EAB6E1B4521F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,12 +19,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$CA$68</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="308">
   <si>
     <t>Roll No</t>
   </si>
@@ -806,24 +819,6 @@
     <t>Noor Fatima</t>
   </si>
   <si>
-    <t>Tehfeez ul Quran (2nd)</t>
-  </si>
-  <si>
-    <t>49.5</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>175.5</t>
-  </si>
-  <si>
-    <t>70.20</t>
-  </si>
-  <si>
     <t>002530</t>
   </si>
   <si>
@@ -963,6 +958,9 @@
   </si>
   <si>
     <t>Homecnomics</t>
+  </si>
+  <si>
+    <t>Tehfeez-ul-Quran</t>
   </si>
 </sst>
 </file>
@@ -978,15 +976,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -994,13 +998,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5009,8 +5039,8 @@
       <c r="M39">
         <v>83.5</v>
       </c>
-      <c r="P39">
-        <v>40.5</v>
+      <c r="P39" t="s">
+        <v>97</v>
       </c>
       <c r="R39">
         <v>57</v>
@@ -5656,8 +5686,8 @@
       <c r="P46">
         <v>30</v>
       </c>
-      <c r="R46" t="s">
-        <v>97</v>
+      <c r="R46">
+        <v>50</v>
       </c>
       <c r="S46">
         <v>43.5</v>
@@ -7721,91 +7751,61 @@
       </c>
     </row>
     <row r="69" spans="1:88" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+      <c r="A69" s="2" t="s">
         <v>258</v>
       </c>
       <c r="B69" t="s">
         <v>259</v>
       </c>
-      <c r="D69" t="s">
-        <v>260</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="D69" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F69" t="s">
-        <v>42</v>
-      </c>
-      <c r="G69" t="s">
-        <v>42</v>
-      </c>
-      <c r="H69" t="s">
-        <v>42</v>
-      </c>
+      <c r="H69" s="4"/>
       <c r="I69" t="s">
         <v>54</v>
       </c>
-      <c r="J69" t="s">
-        <v>106</v>
-      </c>
-      <c r="K69" t="s">
-        <v>261</v>
-      </c>
-      <c r="L69" t="s">
-        <v>262</v>
-      </c>
-      <c r="M69" t="s">
-        <v>263</v>
-      </c>
-      <c r="AG69" t="s">
-        <v>263</v>
-      </c>
-      <c r="AH69" t="s">
-        <v>264</v>
-      </c>
-      <c r="AI69" t="s">
-        <v>265</v>
-      </c>
-      <c r="AJ69" t="s">
-        <v>97</v>
-      </c>
-      <c r="CB69" t="s">
-        <v>36</v>
-      </c>
-      <c r="CC69" t="s">
-        <v>36</v>
-      </c>
-      <c r="CD69" t="s">
-        <v>36</v>
-      </c>
-      <c r="CE69" t="s">
-        <v>36</v>
-      </c>
-      <c r="CF69" t="s">
-        <v>36</v>
-      </c>
-      <c r="CG69" t="s">
-        <v>36</v>
-      </c>
-      <c r="CH69" t="s">
-        <v>36</v>
-      </c>
-      <c r="CI69" t="s">
-        <v>36</v>
-      </c>
-      <c r="CJ69" t="s">
-        <v>36</v>
+      <c r="J69" t="str">
+        <f>IF(AI69&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI69&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI69&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI69&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI69&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
+        <v>Well done! You have great potential to achieve even more.</v>
+      </c>
+      <c r="K69" s="5">
+        <v>49.5</v>
+      </c>
+      <c r="L69" s="5">
+        <v>26</v>
+      </c>
+      <c r="M69" s="5">
+        <v>71.5</v>
+      </c>
+      <c r="U69" s="6"/>
+      <c r="AG69" s="5">
+        <v>65</v>
+      </c>
+      <c r="AH69" s="3">
+        <f>SUM(K69:AG69)</f>
+        <v>212</v>
+      </c>
+      <c r="AI69" s="3">
+        <f>(AH69/325)*100</f>
+        <v>65.230769230769226</v>
+      </c>
+      <c r="AJ69" s="3" t="str">
+        <f>IF(AI69&gt;=80, "A+", IF(AI69&gt;=70, "A", IF(AI69&gt;=60, "B", IF(AI69&gt;=50, "C", IF(AI69&gt;=40, "D", "FAIL")))))</f>
+        <v>B</v>
       </c>
     </row>
     <row r="70" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B70" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="E70" t="s">
         <v>41</v>
@@ -7876,16 +7876,16 @@
     </row>
     <row r="71" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B71" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C71" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D71" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E71" t="s">
         <v>41</v>
@@ -7956,16 +7956,16 @@
     </row>
     <row r="72" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B72" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C72" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D72" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E72" t="s">
         <v>41</v>
@@ -8036,16 +8036,16 @@
     </row>
     <row r="73" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B73" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C73" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="D73" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E73" t="s">
         <v>41</v>
@@ -8116,25 +8116,25 @@
     </row>
     <row r="74" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B74" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C74" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D74" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E74" t="s">
         <v>41</v>
       </c>
       <c r="F74" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G74" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="H74">
         <v>43834</v>
@@ -8235,7 +8235,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CJ21 A74:CJ75 A72:E72 K72:CJ72 A70:E71 A69:E69 K69:CJ69 A68:E68 G68:CJ68 A73:E73 I73:K73 I72 I70:CJ71 I69 A23:CJ52 A22:J22 L22:CJ22 M73:CJ73 A54:CJ67 A53:J53 L53:CJ53" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CJ21 A74:CJ75 A72:E72 K72:CJ72 A70:E71 A68:E68 G68:CJ68 A73:E73 I73:K73 I72 I70:CJ71 A23:CJ38 A22:J22 L22:CJ22 M73:CJ73 A54:CJ67 A53:J53 L53:CJ53 A47:CJ52 A46:Q46 S46:CJ46 A40:CJ45 A39:O39 Q39:CJ39" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8247,44 +8247,44 @@
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.35">
       <c r="H2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="J2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F3" t="s">
+        <v>282</v>
+      </c>
+      <c r="H3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J3" t="s">
+        <v>284</v>
+      </c>
+      <c r="L3" t="s">
+        <v>285</v>
+      </c>
+      <c r="N3" t="s">
         <v>286</v>
-      </c>
-      <c r="D3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F3" t="s">
-        <v>288</v>
-      </c>
-      <c r="H3" t="s">
-        <v>289</v>
-      </c>
-      <c r="J3" t="s">
-        <v>290</v>
-      </c>
-      <c r="L3" t="s">
-        <v>291</v>
-      </c>
-      <c r="N3" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D4" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="F4" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="H4" t="s">
         <v>10</v>
@@ -8298,10 +8298,10 @@
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D5" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
@@ -8313,7 +8313,7 @@
         <v>12</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" t="s">
@@ -8331,17 +8331,17 @@
         <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="J6" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.35">
@@ -8352,7 +8352,7 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
@@ -8361,19 +8361,19 @@
         <v>18</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D8" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
@@ -8394,13 +8394,13 @@
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D9" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="F9" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="H9" t="s">
         <v>23</v>
@@ -8409,22 +8409,22 @@
         <v>23</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D10" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="J10" t="s">
         <v>27</v>
@@ -8436,13 +8436,13 @@
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D11" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="F11" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="H11" t="s">
         <v>27</v>
@@ -8451,16 +8451,16 @@
         <v>26</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="D12" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="F12" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>31</v>
@@ -8469,29 +8469,29 @@
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="L13" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F18" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="H18" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="J18" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F19" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="H19" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="J19" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="20" spans="6:10" x14ac:dyDescent="0.35">
@@ -8518,24 +8518,24 @@
     </row>
     <row r="22" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F22" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="H22" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="J22" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="23" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F23" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="H23" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="J23" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="24" spans="6:10" x14ac:dyDescent="0.35">
@@ -8543,10 +8543,10 @@
         <v>25</v>
       </c>
       <c r="H24" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="J24" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="25" spans="6:10" x14ac:dyDescent="0.35">
@@ -8554,18 +8554,18 @@
         <v>26</v>
       </c>
       <c r="H25" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J25" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="26" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F26" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="H26" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="J26" t="s">
         <v>27</v>

--- a/data/class.xlsx
+++ b/data/class.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/74b89d8f5a3cedb0/Desktop/folder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_F6A1F43F91D74A179400985AF493EAA9998EB2D8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB3B8485-BAA1-4E37-8CB1-EAB6E1B4521F}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_F6A1F43F91D74A179400985AF493EAA9998EB2D8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A9A624C-A8BA-438A-8350-25ABF0A68570}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -960,7 +960,7 @@
     <t>Homecnomics</t>
   </si>
   <si>
-    <t>Tehfeez-ul-Quran</t>
+    <t>Tehfeez ul Quran (2nd)</t>
   </si>
 </sst>
 </file>
@@ -1019,7 +1019,6 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1031,6 +1030,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1377,6 +1377,7 @@
   <dimension ref="A1:CJ75"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="4" max="4" width="31.58203125" customWidth="1"/>
     <col min="10" max="10" width="54.58203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7751,19 +7752,19 @@
       </c>
     </row>
     <row r="69" spans="1:88" x14ac:dyDescent="0.35">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="1" t="s">
         <v>258</v>
       </c>
       <c r="B69" t="s">
         <v>259</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" t="s">
         <v>307</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E69" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H69" s="4"/>
+      <c r="H69" s="3"/>
       <c r="I69" t="s">
         <v>54</v>
       </c>
@@ -7771,28 +7772,28 @@
         <f>IF(AI69&gt;=80, "Outstanding achievement! You are a shining star of our class.", IF(AI69&gt;=70, "Impressive work! Your dedication is truly paying off.", IF(AI69&gt;=60, "Well done! You have great potential to achieve even more.", IF(AI69&gt;=50, "Good effort! A little more focus will lead to better results.", IF(AI69&gt;=40, "Don't lose heart! With extra hard work, you can improve.", "We believe in you! Let's work together for a strong comeback.")))))</f>
         <v>Well done! You have great potential to achieve even more.</v>
       </c>
-      <c r="K69" s="5">
+      <c r="K69" s="4">
         <v>49.5</v>
       </c>
-      <c r="L69" s="5">
+      <c r="L69" s="4">
         <v>26</v>
       </c>
-      <c r="M69" s="5">
+      <c r="M69" s="4">
         <v>71.5</v>
       </c>
-      <c r="U69" s="6"/>
-      <c r="AG69" s="5">
+      <c r="U69" s="5"/>
+      <c r="AG69" s="4">
         <v>65</v>
       </c>
-      <c r="AH69" s="3">
+      <c r="AH69" s="2">
         <f>SUM(K69:AG69)</f>
         <v>212</v>
       </c>
-      <c r="AI69" s="3">
+      <c r="AI69" s="2">
         <f>(AH69/325)*100</f>
         <v>65.230769230769226</v>
       </c>
-      <c r="AJ69" s="3" t="str">
+      <c r="AJ69" s="2" t="str">
         <f>IF(AI69&gt;=80, "A+", IF(AI69&gt;=70, "A", IF(AI69&gt;=60, "B", IF(AI69&gt;=50, "C", IF(AI69&gt;=40, "D", "FAIL")))))</f>
         <v>B</v>
       </c>
@@ -8312,10 +8313,10 @@
       <c r="J5" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="M5" s="1"/>
+      <c r="M5" s="6"/>
       <c r="N5" t="s">
         <v>12</v>
       </c>
@@ -8336,10 +8337,10 @@
       <c r="J6" t="s">
         <v>290</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="1"/>
+      <c r="M6" s="6"/>
       <c r="N6" t="s">
         <v>290</v>
       </c>
@@ -8360,10 +8361,10 @@
       <c r="J7" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="M7" s="1"/>
+      <c r="M7" s="6"/>
       <c r="N7" t="s">
         <v>288</v>
       </c>
@@ -8384,10 +8385,10 @@
       <c r="J8" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="M8" s="1"/>
+      <c r="M8" s="6"/>
       <c r="N8" t="s">
         <v>32</v>
       </c>
@@ -8408,10 +8409,10 @@
       <c r="J9" t="s">
         <v>23</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="M9" s="1"/>
+      <c r="M9" s="6"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
@@ -8429,10 +8430,10 @@
       <c r="J10" t="s">
         <v>27</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="M10" s="1"/>
+      <c r="M10" s="6"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
@@ -8450,10 +8451,10 @@
       <c r="J11" t="s">
         <v>26</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="L11" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="M11" s="1"/>
+      <c r="M11" s="6"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="D12" t="s">
@@ -8462,10 +8463,10 @@
       <c r="F12" t="s">
         <v>288</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="L12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="M12" s="1"/>
+      <c r="M12" s="6"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="L13" t="s">
